--- a/nexus_demo_dataset.xlsx
+++ b/nexus_demo_dataset.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9688" uniqueCount="2193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9767" uniqueCount="2209">
   <si>
     <t>Nexus Data Infrastructure - K-Nexus demo dataset</t>
   </si>
@@ -5849,6 +5849,9 @@
     <t>failure_mode</t>
   </si>
   <si>
+    <t>impact</t>
+  </si>
+  <si>
     <t>match_terms</t>
   </si>
   <si>
@@ -5864,6 +5867,9 @@
     <t>Battery string degradation</t>
   </si>
   <si>
+    <t>outage</t>
+  </si>
+  <si>
     <t>resistance trending|capacity fade|Battery batch</t>
   </si>
   <si>
@@ -5909,6 +5915,9 @@
     <t>Filter loading</t>
   </si>
   <si>
+    <t>efficiency</t>
+  </si>
+  <si>
     <t>Filter differential pressure</t>
   </si>
   <si>
@@ -5918,13 +5927,34 @@
     <t>Compare fan power draw against the commissioning baseline</t>
   </si>
   <si>
+    <t>RB-CHL-TRIP</t>
+  </si>
+  <si>
+    <t>Chiller trip on condenser scaling</t>
+  </si>
+  <si>
+    <t>scale build-up|Cooling water quality</t>
+  </si>
+  <si>
+    <t>Start the standby chiller and confirm chilled-water supply temperature</t>
+  </si>
+  <si>
+    <t>Check rack inlet temperatures in every hall the plant serves</t>
+  </si>
+  <si>
+    <t>Dose descalant and schedule mechanical tube cleaning</t>
+  </si>
+  <si>
+    <t>Review make-up water treatment against the hardness trend</t>
+  </si>
+  <si>
     <t>RB-CHL-APP</t>
   </si>
   <si>
     <t>Condenser approach degrading</t>
   </si>
   <si>
-    <t>Approach temperature|scale build-up</t>
+    <t>Approach temperature</t>
   </si>
   <si>
     <t>Trend condenser approach against the 2.8 C design value</t>
@@ -5945,7 +5975,7 @@
     <t>Make-up water shortfall</t>
   </si>
   <si>
-    <t>Make-up water|Municipal supply|WUE</t>
+    <t>Make-up water|Municipal supply</t>
   </si>
   <si>
     <t>Switch make-up to treated-water storage and confirm hours of reserve</t>
@@ -5957,7 +5987,22 @@
     <t>Raise cycles of concentration within chemistry limits</t>
   </si>
   <si>
-    <t>File the state water-impact disclosure if the WUE breach is reportable</t>
+    <t>RB-CT-WUE</t>
+  </si>
+  <si>
+    <t>Water use above reporting target</t>
+  </si>
+  <si>
+    <t>compliance</t>
+  </si>
+  <si>
+    <t>WUE</t>
+  </si>
+  <si>
+    <t>Confirm the WUE reading against the make-up and blowdown meters</t>
+  </si>
+  <si>
+    <t>File the state water-impact disclosure with the corrective plan</t>
   </si>
   <si>
     <t>RB-CHW-DP</t>
@@ -6063,6 +6108,9 @@
   </si>
   <si>
     <t>Steps run in order. within_min is the target time from detection to completing the step.</t>
+  </si>
+  <si>
+    <t>impact: outage (tenant SLAs at stake), capacity (growth blocked), compliance (reportable breach), efficiency (energy and cost).</t>
   </si>
   <si>
     <t>Owner teams are the teams already named in 20_active_alerts.</t>
@@ -11908,7 +11956,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
         <v>1493</v>
       </c>
@@ -13423,7 +13471,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
         <v>1508</v>
       </c>
@@ -21066,18 +21114,18 @@
   <sheetData>
     <row r="1" ht="17.35" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>2171</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>2172</v>
+        <v>2188</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>2173</v>
+        <v>2189</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>2174</v>
+        <v>2190</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>50</v>
@@ -21085,7 +21133,7 @@
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>2175</v>
+        <v>2191</v>
       </c>
       <c r="B4" s="6">
         <f>SUMIFS(03_rows!O2:O25,03_rows!Q2:Q25,"structural")</f>
@@ -21101,7 +21149,7 @@
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>2176</v>
+        <v>2192</v>
       </c>
       <c r="B5" s="6">
         <f>SUMIFS(03_rows!O2:O25,03_rows!Q2:Q25,"planned headroom")</f>
@@ -21117,7 +21165,7 @@
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>2177</v>
+        <v>2193</v>
       </c>
       <c r="B6" s="6">
         <f>SUM(03_rows!H2:H25)</f>
@@ -21133,7 +21181,7 @@
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>2178</v>
+        <v>2194</v>
       </c>
       <c r="B7" s="6">
         <f>SUMIFS(03_rows!G2:G25,03_rows!B2:B25,"MUM-1-H4")</f>
@@ -21149,7 +21197,7 @@
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>2179</v>
+        <v>2195</v>
       </c>
       <c r="B8" s="6">
         <f>SUMIFS(03_rows!I2:I25,03_rows!B2:B25,"MUM-1-H4")-SUMIFS(03_rows!H2:H25,03_rows!B2:B25,"MUM-1-H4")</f>
@@ -21165,7 +21213,7 @@
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>2180</v>
+        <v>2196</v>
       </c>
       <c r="B9" s="6">
         <f>SUMIFS(03_rows!J2:J25,03_rows!B2:B25,"MUM-1-H4")-SUMIFS(03_rows!H2:H25,03_rows!B2:B25,"MUM-1-H4")</f>
@@ -21181,7 +21229,7 @@
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>2181</v>
+        <v>2197</v>
       </c>
       <c r="B10" s="6">
         <f>COUNTIFS(07_cascade_result!K2:K13,"exceeded")</f>
@@ -21197,7 +21245,7 @@
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>2182</v>
+        <v>2198</v>
       </c>
       <c r="B11" s="6">
         <f>COUNTIFS(07_cascade_result!K2:K13,"redundancy_lost")</f>
@@ -21213,7 +21261,7 @@
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>2183</v>
+        <v>2199</v>
       </c>
       <c r="B12" s="6">
         <f>SUM(06_upgrade_options!D2:D7)</f>
@@ -21229,7 +21277,7 @@
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>2184</v>
+        <v>2200</v>
       </c>
       <c r="B13" s="6">
         <f>MAX(06_upgrade_options!E2:E7)</f>
@@ -21245,7 +21293,7 @@
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>2185</v>
+        <v>2201</v>
       </c>
       <c r="B14" s="6">
         <f>SUM(01_facilities!J2:J7)</f>
@@ -21261,7 +21309,7 @@
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>2186</v>
+        <v>2202</v>
       </c>
       <c r="B15" s="6">
         <f>COUNTA(04_racks!A2:A481)</f>
@@ -21277,7 +21325,7 @@
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>2187</v>
+        <v>2203</v>
       </c>
       <c r="B16" s="6">
         <f>ROUND(SUM(04_racks!N2:N481),0)</f>
@@ -21293,7 +21341,7 @@
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>2188</v>
+        <v>2204</v>
       </c>
       <c r="B17" s="6">
         <f>COUNTIFS(04_racks!O2:O481,"occupied")</f>
@@ -21309,7 +21357,7 @@
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>2189</v>
+        <v>2205</v>
       </c>
       <c r="B18" s="6">
         <f>COUNTIFS(04_racks!C2:C481,"MUM-1-H4",04_racks!O2:O481,"free")</f>
@@ -21325,7 +21373,7 @@
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>2190</v>
+        <v>2206</v>
       </c>
       <c r="B19" s="6">
         <f>COUNTIFS(04_racks!O2:O481,"blocked")</f>
@@ -21341,7 +21389,7 @@
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>2191</v>
+        <v>2207</v>
       </c>
       <c r="B20" s="6">
         <f>COUNTA(04b_component_positions!A2:A149)</f>
@@ -21357,7 +21405,7 @@
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>2192</v>
+        <v>2208</v>
       </c>
     </row>
   </sheetData>
@@ -21368,20 +21416,21 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="44" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="72" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="44" customWidth="1"/>
+    <col min="6" max="6" width="6" customWidth="1"/>
+    <col min="7" max="7" width="72" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>1933</v>
       </c>
@@ -21398,933 +21447,1220 @@
         <v>1936</v>
       </c>
       <c r="F1" s="5" t="s">
+        <v>1937</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>1576</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>1830</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>1937</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="5" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>831</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>1940</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>1942</v>
+      </c>
+      <c r="F2" s="8">
+        <v>1</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>1943</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>1842</v>
+      </c>
+      <c r="I2" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
         <v>1939</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>1940</v>
-      </c>
-      <c r="E2" s="8">
-        <v>1</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>1941</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>1842</v>
-      </c>
-      <c r="H2" s="8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>1938</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>831</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>1940</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>1942</v>
+      </c>
+      <c r="F3" s="8">
+        <v>2</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>1944</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>1842</v>
+      </c>
+      <c r="I3" s="8">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>1939</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>1940</v>
-      </c>
-      <c r="E3" s="8">
-        <v>2</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>1942</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>1842</v>
-      </c>
-      <c r="H3" s="8">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>1938</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>831</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>1940</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>1942</v>
+      </c>
+      <c r="F4" s="8">
+        <v>3</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>1945</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>1871</v>
+      </c>
+      <c r="I4" s="8">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>1939</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>1940</v>
-      </c>
-      <c r="E4" s="8">
-        <v>3</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>1943</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>1871</v>
-      </c>
-      <c r="H4" s="8">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>1938</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>831</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>1940</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>1942</v>
+      </c>
+      <c r="F5" s="8">
+        <v>4</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>1946</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="8">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>1939</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>1940</v>
-      </c>
-      <c r="E5" s="8">
-        <v>4</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>1944</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="H5" s="8">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>1938</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>831</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1940</v>
-      </c>
-      <c r="E6" s="8">
+        <v>1941</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>1942</v>
+      </c>
+      <c r="F6" s="8">
         <v>5</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>1945</v>
-      </c>
       <c r="G6" s="6" t="s">
+        <v>1947</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>1842</v>
       </c>
-      <c r="H6" s="8">
+      <c r="I6" s="8">
         <v>1440</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>1946</v>
+        <v>1948</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>988</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="D7" s="6" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F7" s="8">
+        <v>1</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>1951</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I7" s="8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
         <v>1948</v>
-      </c>
-      <c r="E7" s="8">
-        <v>1</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>1949</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="H7" s="8">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>1946</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>988</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="D8" s="6" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F8" s="8">
+        <v>2</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>1952</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
         <v>1948</v>
-      </c>
-      <c r="E8" s="8">
-        <v>2</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>1950</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="H8" s="8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>1946</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>988</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="D9" s="6" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F9" s="8">
+        <v>3</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>1953</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="8">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
         <v>1948</v>
-      </c>
-      <c r="E9" s="8">
-        <v>3</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>1951</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="H9" s="8">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>1946</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>988</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1948</v>
-      </c>
-      <c r="E10" s="8">
+        <v>1941</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F10" s="8">
         <v>4</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>1952</v>
-      </c>
       <c r="G10" s="6" t="s">
+        <v>1954</v>
+      </c>
+      <c r="H10" s="6" t="s">
         <v>1880</v>
       </c>
-      <c r="H10" s="8">
+      <c r="I10" s="8">
         <v>1440</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>1953</v>
+        <v>1955</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>988</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="D11" s="6" t="s">
+        <v>1957</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>1958</v>
+      </c>
+      <c r="F11" s="8">
+        <v>1</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>1959</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I11" s="8">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
         <v>1955</v>
-      </c>
-      <c r="E11" s="8">
-        <v>1</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>1956</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="H11" s="8">
-        <v>1440</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>1953</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>988</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1955</v>
-      </c>
-      <c r="E12" s="8">
+        <v>1957</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>1958</v>
+      </c>
+      <c r="F12" s="8">
         <v>2</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>1957</v>
-      </c>
       <c r="G12" s="6" t="s">
+        <v>1960</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="8">
+      <c r="I12" s="8">
         <v>2880</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>1958</v>
+        <v>1961</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>977</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>1959</v>
+        <v>1962</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1960</v>
-      </c>
-      <c r="E13" s="8">
+        <v>1941</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>1963</v>
+      </c>
+      <c r="F13" s="8">
         <v>1</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="G13" s="6" t="s">
+        <v>1964</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>1961</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="H13" s="8">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>1958</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>977</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1959</v>
+        <v>1962</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1960</v>
-      </c>
-      <c r="E14" s="8">
+        <v>1941</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>1963</v>
+      </c>
+      <c r="F14" s="8">
         <v>2</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>1962</v>
-      </c>
       <c r="G14" s="6" t="s">
+        <v>1965</v>
+      </c>
+      <c r="H14" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="8">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I14" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>1958</v>
+        <v>1961</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>977</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>1959</v>
+        <v>1962</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1960</v>
-      </c>
-      <c r="E15" s="8">
+        <v>1941</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>1963</v>
+      </c>
+      <c r="F15" s="8">
         <v>3</v>
       </c>
-      <c r="F15" s="6" t="s">
-        <v>1963</v>
-      </c>
       <c r="G15" s="6" t="s">
+        <v>1966</v>
+      </c>
+      <c r="H15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H15" s="8">
-        <v>10080</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I15" s="8">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>1958</v>
+        <v>1961</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>977</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>1959</v>
+        <v>1962</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1960</v>
-      </c>
-      <c r="E16" s="8">
+        <v>1941</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>1963</v>
+      </c>
+      <c r="F16" s="8">
         <v>4</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>1964</v>
-      </c>
       <c r="G16" s="6" t="s">
+        <v>1967</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="8">
+        <v>4320</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>1968</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>977</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>1969</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>1957</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F17" s="8">
+        <v>1</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>1971</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="8">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>1968</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>977</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>1969</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>1957</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F18" s="8">
+        <v>2</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>1972</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="8">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>1968</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>977</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>1969</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>1957</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F19" s="8">
+        <v>3</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>1973</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="8">
+        <v>10080</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>1968</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>977</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>1969</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>1957</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F20" s="8">
+        <v>4</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>1974</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>1885</v>
       </c>
-      <c r="H16" s="8">
+      <c r="I20" s="8">
         <v>10080</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>1965</v>
-      </c>
-      <c r="B17" s="6" t="s">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>970</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>1966</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>1967</v>
-      </c>
-      <c r="E17" s="8">
+      <c r="C21" s="6" t="s">
+        <v>1976</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>1977</v>
+      </c>
+      <c r="F21" s="8">
         <v>1</v>
       </c>
-      <c r="F17" s="6" t="s">
-        <v>1968</v>
-      </c>
-      <c r="G17" s="6" t="s">
+      <c r="G21" s="6" t="s">
+        <v>1978</v>
+      </c>
+      <c r="H21" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H17" s="8">
+      <c r="I21" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>1965</v>
-      </c>
-      <c r="B18" s="6" t="s">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>970</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>1966</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>1967</v>
-      </c>
-      <c r="E18" s="8">
+      <c r="C22" s="6" t="s">
+        <v>1976</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>1977</v>
+      </c>
+      <c r="F22" s="8">
         <v>2</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>1969</v>
-      </c>
-      <c r="G18" s="6" t="s">
+      <c r="G22" s="6" t="s">
+        <v>1979</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H18" s="8">
+      <c r="I22" s="8">
         <v>240</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>1965</v>
-      </c>
-      <c r="B19" s="6" t="s">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>970</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>1966</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>1967</v>
-      </c>
-      <c r="E19" s="8">
+      <c r="C23" s="6" t="s">
+        <v>1976</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>1977</v>
+      </c>
+      <c r="F23" s="8">
         <v>3</v>
       </c>
-      <c r="F19" s="6" t="s">
-        <v>1970</v>
-      </c>
-      <c r="G19" s="6" t="s">
+      <c r="G23" s="6" t="s">
+        <v>1980</v>
+      </c>
+      <c r="H23" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H19" s="8">
+      <c r="I23" s="8">
         <v>480</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>1965</v>
-      </c>
-      <c r="B20" s="6" t="s">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>970</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>1966</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>1967</v>
-      </c>
-      <c r="E20" s="8">
-        <v>4</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>1971</v>
-      </c>
-      <c r="G20" s="6" t="s">
+      <c r="C24" s="6" t="s">
+        <v>1982</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>1983</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>1984</v>
+      </c>
+      <c r="F24" s="8">
+        <v>1</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>1985</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>1885</v>
       </c>
-      <c r="H20" s="8">
+      <c r="I24" s="8">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>970</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>1982</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>1983</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>1984</v>
+      </c>
+      <c r="F25" s="8">
+        <v>2</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>1980</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I25" s="8">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>970</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>1982</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>1983</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>1984</v>
+      </c>
+      <c r="F26" s="8">
+        <v>3</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>1986</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>1885</v>
+      </c>
+      <c r="I26" s="8">
         <v>4320</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>1972</v>
-      </c>
-      <c r="B21" s="6" t="s">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>1987</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>982</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>1973</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>1974</v>
-      </c>
-      <c r="E21" s="8">
+      <c r="C27" s="6" t="s">
+        <v>1988</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>1957</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>1989</v>
+      </c>
+      <c r="F27" s="8">
         <v>1</v>
       </c>
-      <c r="F21" s="6" t="s">
-        <v>1975</v>
-      </c>
-      <c r="G21" s="6" t="s">
+      <c r="G27" s="6" t="s">
+        <v>1990</v>
+      </c>
+      <c r="H27" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H21" s="8">
+      <c r="I27" s="8">
         <v>240</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>1972</v>
-      </c>
-      <c r="B22" s="6" t="s">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>1987</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>982</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>1973</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>1974</v>
-      </c>
-      <c r="E22" s="8">
+      <c r="C28" s="6" t="s">
+        <v>1988</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>1957</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>1989</v>
+      </c>
+      <c r="F28" s="8">
         <v>2</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>1976</v>
-      </c>
-      <c r="G22" s="6" t="s">
+      <c r="G28" s="6" t="s">
+        <v>1991</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H22" s="8">
+      <c r="I28" s="8">
         <v>4320</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>1977</v>
-      </c>
-      <c r="B23" s="6" t="s">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>851</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>1978</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>1979</v>
-      </c>
-      <c r="E23" s="8">
+      <c r="C29" s="6" t="s">
+        <v>1993</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>1994</v>
+      </c>
+      <c r="F29" s="8">
         <v>1</v>
       </c>
-      <c r="F23" s="6" t="s">
-        <v>1980</v>
-      </c>
-      <c r="G23" s="6" t="s">
+      <c r="G29" s="6" t="s">
+        <v>1995</v>
+      </c>
+      <c r="H29" s="6" t="s">
         <v>1842</v>
       </c>
-      <c r="H23" s="8">
+      <c r="I29" s="8">
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>1977</v>
-      </c>
-      <c r="B24" s="6" t="s">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>851</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>1978</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>1979</v>
-      </c>
-      <c r="E24" s="8">
+      <c r="C30" s="6" t="s">
+        <v>1993</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>1994</v>
+      </c>
+      <c r="F30" s="8">
         <v>2</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>1981</v>
-      </c>
-      <c r="G24" s="6" t="s">
+      <c r="G30" s="6" t="s">
+        <v>1996</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>1842</v>
       </c>
-      <c r="H24" s="8">
+      <c r="I30" s="8">
         <v>1440</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>1977</v>
-      </c>
-      <c r="B25" s="6" t="s">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>851</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>1978</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>1979</v>
-      </c>
-      <c r="E25" s="8">
+      <c r="C31" s="6" t="s">
+        <v>1993</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>1994</v>
+      </c>
+      <c r="F31" s="8">
         <v>3</v>
       </c>
-      <c r="F25" s="6" t="s">
-        <v>1982</v>
-      </c>
-      <c r="G25" s="6" t="s">
+      <c r="G31" s="6" t="s">
+        <v>1997</v>
+      </c>
+      <c r="H31" s="6" t="s">
         <v>1842</v>
       </c>
-      <c r="H25" s="8">
+      <c r="I31" s="8">
         <v>4320</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>1983</v>
-      </c>
-      <c r="B26" s="6" t="s">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>1998</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>854</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>1984</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>1985</v>
-      </c>
-      <c r="E26" s="8">
+      <c r="C32" s="6" t="s">
+        <v>1999</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>2000</v>
+      </c>
+      <c r="F32" s="8">
         <v>1</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>1986</v>
-      </c>
-      <c r="G26" s="6" t="s">
+      <c r="G32" s="6" t="s">
+        <v>2001</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>1880</v>
       </c>
-      <c r="H26" s="8">
+      <c r="I32" s="8">
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>1983</v>
-      </c>
-      <c r="B27" s="6" t="s">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>1998</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>854</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>1984</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>1985</v>
-      </c>
-      <c r="E27" s="8">
+      <c r="C33" s="6" t="s">
+        <v>1999</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>2000</v>
+      </c>
+      <c r="F33" s="8">
         <v>2</v>
       </c>
-      <c r="F27" s="6" t="s">
-        <v>1987</v>
-      </c>
-      <c r="G27" s="6" t="s">
+      <c r="G33" s="6" t="s">
+        <v>2002</v>
+      </c>
+      <c r="H33" s="6" t="s">
         <v>1880</v>
       </c>
-      <c r="H27" s="8">
+      <c r="I33" s="8">
         <v>4320</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>1983</v>
-      </c>
-      <c r="B28" s="6" t="s">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
+        <v>1998</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>854</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>1984</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>1985</v>
-      </c>
-      <c r="E28" s="8">
+      <c r="C34" s="6" t="s">
+        <v>1999</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>2000</v>
+      </c>
+      <c r="F34" s="8">
         <v>3</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>1988</v>
-      </c>
-      <c r="G28" s="6" t="s">
+      <c r="G34" s="6" t="s">
+        <v>2003</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>1880</v>
       </c>
-      <c r="H28" s="8">
+      <c r="I34" s="8">
         <v>10080</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>1989</v>
-      </c>
-      <c r="B29" s="6" t="s">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>2004</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>818</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>1990</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>1991</v>
-      </c>
-      <c r="E29" s="8">
+      <c r="C35" s="6" t="s">
+        <v>2005</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F35" s="8">
         <v>1</v>
       </c>
-      <c r="F29" s="6" t="s">
-        <v>1992</v>
-      </c>
-      <c r="G29" s="6" t="s">
+      <c r="G35" s="6" t="s">
+        <v>2007</v>
+      </c>
+      <c r="H35" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="8">
+      <c r="I35" s="8">
         <v>240</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>1989</v>
-      </c>
-      <c r="B30" s="6" t="s">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
+        <v>2004</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>818</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>1990</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>1991</v>
-      </c>
-      <c r="E30" s="8">
+      <c r="C36" s="6" t="s">
+        <v>2005</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F36" s="8">
         <v>2</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>1993</v>
-      </c>
-      <c r="G30" s="6" t="s">
+      <c r="G36" s="6" t="s">
+        <v>2008</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>1842</v>
       </c>
-      <c r="H30" s="8">
+      <c r="I36" s="8">
         <v>1440</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
-        <v>1989</v>
-      </c>
-      <c r="B31" s="6" t="s">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
+        <v>2004</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>818</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>1990</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>1991</v>
-      </c>
-      <c r="E31" s="8">
+      <c r="C37" s="6" t="s">
+        <v>2005</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F37" s="8">
         <v>3</v>
       </c>
-      <c r="F31" s="6" t="s">
-        <v>1994</v>
-      </c>
-      <c r="G31" s="6" t="s">
+      <c r="G37" s="6" t="s">
+        <v>2009</v>
+      </c>
+      <c r="H37" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H31" s="8">
+      <c r="I37" s="8">
         <v>10080</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>1995</v>
-      </c>
-      <c r="B32" s="6" t="s">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>802</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>1996</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>1997</v>
-      </c>
-      <c r="E32" s="8">
+      <c r="C38" s="6" t="s">
+        <v>2011</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>2012</v>
+      </c>
+      <c r="F38" s="8">
         <v>1</v>
       </c>
-      <c r="F32" s="6" t="s">
-        <v>1998</v>
-      </c>
-      <c r="G32" s="6" t="s">
+      <c r="G38" s="6" t="s">
+        <v>2013</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>1880</v>
       </c>
-      <c r="H32" s="8">
+      <c r="I38" s="8">
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
-        <v>1995</v>
-      </c>
-      <c r="B33" s="6" t="s">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B39" s="6" t="s">
         <v>802</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>1996</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>1997</v>
-      </c>
-      <c r="E33" s="8">
+      <c r="C39" s="6" t="s">
+        <v>2011</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>2012</v>
+      </c>
+      <c r="F39" s="8">
         <v>2</v>
       </c>
-      <c r="F33" s="6" t="s">
-        <v>1999</v>
-      </c>
-      <c r="G33" s="6" t="s">
+      <c r="G39" s="6" t="s">
+        <v>2014</v>
+      </c>
+      <c r="H39" s="6" t="s">
         <v>1880</v>
       </c>
-      <c r="H33" s="8">
+      <c r="I39" s="8">
         <v>1440</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
-        <v>1995</v>
-      </c>
-      <c r="B34" s="6" t="s">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>802</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>1996</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>1997</v>
-      </c>
-      <c r="E34" s="8">
+      <c r="C40" s="6" t="s">
+        <v>2011</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>2012</v>
+      </c>
+      <c r="F40" s="8">
         <v>3</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>2000</v>
-      </c>
-      <c r="G34" s="6" t="s">
+      <c r="G40" s="6" t="s">
+        <v>2015</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>1871</v>
       </c>
-      <c r="H34" s="8">
+      <c r="I40" s="8">
         <v>10080</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
-        <v>2001</v>
-      </c>
-      <c r="B35" s="6" t="s">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="6" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>1062</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>2002</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>2003</v>
-      </c>
-      <c r="E35" s="8">
+      <c r="C41" s="6" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>2018</v>
+      </c>
+      <c r="F41" s="8">
         <v>1</v>
       </c>
-      <c r="F35" s="6" t="s">
-        <v>2004</v>
-      </c>
-      <c r="G35" s="6" t="s">
+      <c r="G41" s="6" t="s">
+        <v>2019</v>
+      </c>
+      <c r="H41" s="6" t="s">
         <v>1880</v>
       </c>
-      <c r="H35" s="8">
+      <c r="I41" s="8">
         <v>1440</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
-        <v>2001</v>
-      </c>
-      <c r="B36" s="6" t="s">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="6" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>1062</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>2002</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>2003</v>
-      </c>
-      <c r="E36" s="8">
+      <c r="C42" s="6" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>2018</v>
+      </c>
+      <c r="F42" s="8">
         <v>2</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>2005</v>
-      </c>
-      <c r="G36" s="6" t="s">
+      <c r="G42" s="6" t="s">
+        <v>2020</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>1880</v>
       </c>
-      <c r="H36" s="8">
+      <c r="I42" s="8">
         <v>4320</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="9" t="s">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="9" t="s">
-        <v>2007</v>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="9" t="s">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="9" t="s">
+        <v>2023</v>
       </c>
     </row>
   </sheetData>
@@ -22353,25 +22689,25 @@
         <v>42</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>2008</v>
+        <v>2024</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>2009</v>
+        <v>2025</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>2010</v>
+        <v>2026</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>2011</v>
+        <v>2027</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>2012</v>
+        <v>2028</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>2013</v>
+        <v>2029</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>2014</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -22379,7 +22715,7 @@
         <v>61</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>2015</v>
+        <v>2031</v>
       </c>
       <c r="C2" s="8">
         <v>4</v>
@@ -22397,7 +22733,7 @@
         <v>18</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>2016</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -22405,7 +22741,7 @@
         <v>69</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>2015</v>
+        <v>2031</v>
       </c>
       <c r="C3" s="8">
         <v>4</v>
@@ -22423,7 +22759,7 @@
         <v>23</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>2017</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -22431,7 +22767,7 @@
         <v>73</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>2015</v>
+        <v>2031</v>
       </c>
       <c r="C4" s="8">
         <v>4</v>
@@ -22449,7 +22785,7 @@
         <v>27</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>2018</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -22457,7 +22793,7 @@
         <v>79</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>2019</v>
+        <v>2035</v>
       </c>
       <c r="C5" s="8">
         <v>3</v>
@@ -22475,7 +22811,7 @@
         <v>11</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>2020</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -22483,7 +22819,7 @@
         <v>85</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>2021</v>
+        <v>2037</v>
       </c>
       <c r="C6" s="8">
         <v>2</v>
@@ -22501,7 +22837,7 @@
         <v>34</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>2022</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -22509,7 +22845,7 @@
         <v>91</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>2019</v>
+        <v>2035</v>
       </c>
       <c r="C7" s="8">
         <v>3</v>
@@ -22523,22 +22859,22 @@
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6" t="s">
-        <v>2023</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>2024</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>2025</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>2026</v>
+        <v>2042</v>
       </c>
     </row>
   </sheetData>
@@ -22566,22 +22902,22 @@
         <v>789</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>2027</v>
+        <v>2043</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>2028</v>
+        <v>2044</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>2029</v>
+        <v>2045</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>800</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>2030</v>
+        <v>2046</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>2031</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -22589,13 +22925,13 @@
         <v>831</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>2032</v>
+        <v>2048</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>2033</v>
+        <v>2049</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>2034</v>
+        <v>2050</v>
       </c>
       <c r="E2" s="8">
         <v>16</v>
@@ -22604,7 +22940,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>2035</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -22612,13 +22948,13 @@
         <v>854</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>2036</v>
+        <v>2052</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>2037</v>
+        <v>2053</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>2038</v>
+        <v>2054</v>
       </c>
       <c r="E3" s="8">
         <v>10</v>
@@ -22627,7 +22963,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>2039</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -22635,13 +22971,13 @@
         <v>847</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>2036</v>
+        <v>2052</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>2037</v>
+        <v>2053</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>2038</v>
+        <v>2054</v>
       </c>
       <c r="E4" s="8">
         <v>9</v>
@@ -22650,7 +22986,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>2040</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -22658,13 +22994,13 @@
         <v>851</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>2041</v>
+        <v>2057</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>2042</v>
+        <v>2058</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>2034</v>
+        <v>2050</v>
       </c>
       <c r="E5" s="8">
         <v>14</v>
@@ -22673,7 +23009,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>2043</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -22681,13 +23017,13 @@
         <v>988</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>2044</v>
+        <v>2060</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>2045</v>
+        <v>2061</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>2038</v>
+        <v>2054</v>
       </c>
       <c r="E6" s="8">
         <v>8</v>
@@ -22696,7 +23032,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>2046</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -22704,13 +23040,13 @@
         <v>977</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>2047</v>
+        <v>2063</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>2048</v>
+        <v>2064</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>2034</v>
+        <v>2050</v>
       </c>
       <c r="E7" s="8">
         <v>22</v>
@@ -22719,7 +23055,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>2049</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -22727,13 +23063,13 @@
         <v>970</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>2050</v>
+        <v>2066</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>2037</v>
+        <v>2053</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>2038</v>
+        <v>2054</v>
       </c>
       <c r="E8" s="8">
         <v>12</v>
@@ -22742,7 +23078,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>2051</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -22750,13 +23086,13 @@
         <v>982</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>2050</v>
+        <v>2066</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>2037</v>
+        <v>2053</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>2038</v>
+        <v>2054</v>
       </c>
       <c r="E9" s="8">
         <v>6</v>
@@ -22765,7 +23101,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>2052</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -22773,13 +23109,13 @@
         <v>818</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>2053</v>
+        <v>2069</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>2070</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>2054</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>2038</v>
       </c>
       <c r="E10" s="8">
         <v>26</v>
@@ -22788,7 +23124,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>2055</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -22796,13 +23132,13 @@
         <v>812</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>2056</v>
+        <v>2072</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>2037</v>
+        <v>2053</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>2038</v>
+        <v>2054</v>
       </c>
       <c r="E11" s="8">
         <v>34</v>
@@ -22811,7 +23147,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>2057</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -22819,13 +23155,13 @@
         <v>826</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>2058</v>
+        <v>2074</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>2059</v>
+        <v>2075</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>2034</v>
+        <v>2050</v>
       </c>
       <c r="E12" s="8">
         <v>20</v>
@@ -22834,17 +23170,17 @@
         <v>0</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>2060</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>2061</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>2062</v>
+        <v>2078</v>
       </c>
     </row>
   </sheetData>
@@ -22870,7 +23206,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>2063</v>
+        <v>2079</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>42</v>
@@ -22885,24 +23221,24 @@
         <v>788</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>2064</v>
+        <v>2080</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>2065</v>
+        <v>2081</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>2066</v>
+        <v>2082</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>2067</v>
+        <v>2083</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>2068</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>2069</v>
+        <v>2085</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>61</v>
@@ -22917,7 +23253,7 @@
         <v>204</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>2070</v>
+        <v>2086</v>
       </c>
       <c r="G2" s="10">
         <v>21.3</v>
@@ -22927,12 +23263,12 @@
         <v>27</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>2072</v>
+        <v>2088</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>61</v>
@@ -22947,7 +23283,7 @@
         <v>216</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>2073</v>
+        <v>2089</v>
       </c>
       <c r="G3" s="10">
         <v>21.9</v>
@@ -22957,12 +23293,12 @@
         <v>27</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>2074</v>
+        <v>2090</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>61</v>
@@ -22977,7 +23313,7 @@
         <v>229</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>2070</v>
+        <v>2086</v>
       </c>
       <c r="G4" s="10">
         <v>21.3</v>
@@ -22987,12 +23323,12 @@
         <v>27</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>2075</v>
+        <v>2091</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>61</v>
@@ -23007,7 +23343,7 @@
         <v>241</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>2073</v>
+        <v>2089</v>
       </c>
       <c r="G5" s="8">
         <v>22</v>
@@ -23017,12 +23353,12 @@
         <v>27</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>2076</v>
+        <v>2092</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>61</v>
@@ -23037,7 +23373,7 @@
         <v>254</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>2070</v>
+        <v>2086</v>
       </c>
       <c r="G6" s="10">
         <v>20.9</v>
@@ -23047,12 +23383,12 @@
         <v>27</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>2077</v>
+        <v>2093</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>61</v>
@@ -23067,7 +23403,7 @@
         <v>266</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>2073</v>
+        <v>2089</v>
       </c>
       <c r="G7" s="10">
         <v>21.7</v>
@@ -23077,12 +23413,12 @@
         <v>27</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>2078</v>
+        <v>2094</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>61</v>
@@ -23097,7 +23433,7 @@
         <v>280</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>2070</v>
+        <v>2086</v>
       </c>
       <c r="G8" s="10">
         <v>21.1</v>
@@ -23107,12 +23443,12 @@
         <v>27</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>2079</v>
+        <v>2095</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>61</v>
@@ -23127,7 +23463,7 @@
         <v>292</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>2073</v>
+        <v>2089</v>
       </c>
       <c r="G9" s="8">
         <v>22</v>
@@ -23137,12 +23473,12 @@
         <v>27</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>2080</v>
+        <v>2096</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>61</v>
@@ -23157,7 +23493,7 @@
         <v>305</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>2070</v>
+        <v>2086</v>
       </c>
       <c r="G10" s="10">
         <v>20.9</v>
@@ -23167,12 +23503,12 @@
         <v>27</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>2081</v>
+        <v>2097</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>61</v>
@@ -23187,7 +23523,7 @@
         <v>317</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>2073</v>
+        <v>2089</v>
       </c>
       <c r="G11" s="10">
         <v>21.9</v>
@@ -23197,12 +23533,12 @@
         <v>27</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>2082</v>
+        <v>2098</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>61</v>
@@ -23217,7 +23553,7 @@
         <v>330</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>2070</v>
+        <v>2086</v>
       </c>
       <c r="G12" s="10">
         <v>20.8</v>
@@ -23227,12 +23563,12 @@
         <v>27</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>2083</v>
+        <v>2099</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>61</v>
@@ -23247,7 +23583,7 @@
         <v>342</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>2073</v>
+        <v>2089</v>
       </c>
       <c r="G13" s="10">
         <v>21.9</v>
@@ -23257,12 +23593,12 @@
         <v>27</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>2084</v>
+        <v>2100</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>61</v>
@@ -23277,7 +23613,7 @@
         <v>354</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>2070</v>
+        <v>2086</v>
       </c>
       <c r="G14" s="10">
         <v>21.6</v>
@@ -23287,12 +23623,12 @@
         <v>27</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>2085</v>
+        <v>2101</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>61</v>
@@ -23307,7 +23643,7 @@
         <v>366</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>2073</v>
+        <v>2089</v>
       </c>
       <c r="G15" s="10">
         <v>22.2</v>
@@ -23317,12 +23653,12 @@
         <v>27</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>2086</v>
+        <v>2102</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>61</v>
@@ -23337,7 +23673,7 @@
         <v>378</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>2070</v>
+        <v>2086</v>
       </c>
       <c r="G16" s="10">
         <v>21.2</v>
@@ -23347,12 +23683,12 @@
         <v>27</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>2087</v>
+        <v>2103</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>61</v>
@@ -23367,7 +23703,7 @@
         <v>390</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>2073</v>
+        <v>2089</v>
       </c>
       <c r="G17" s="10">
         <v>21.9</v>
@@ -23377,12 +23713,12 @@
         <v>27</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>2088</v>
+        <v>2104</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>61</v>
@@ -23397,7 +23733,7 @@
         <v>402</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>2070</v>
+        <v>2086</v>
       </c>
       <c r="G18" s="10">
         <v>21.1</v>
@@ -23407,12 +23743,12 @@
         <v>27</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>2089</v>
+        <v>2105</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>61</v>
@@ -23427,7 +23763,7 @@
         <v>414</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>2073</v>
+        <v>2089</v>
       </c>
       <c r="G19" s="10">
         <v>21.9</v>
@@ -23437,12 +23773,12 @@
         <v>27</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>2090</v>
+        <v>2106</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>61</v>
@@ -23457,7 +23793,7 @@
         <v>426</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>2070</v>
+        <v>2086</v>
       </c>
       <c r="G20" s="10">
         <v>20.9</v>
@@ -23467,12 +23803,12 @@
         <v>27</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>2091</v>
+        <v>2107</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>61</v>
@@ -23487,7 +23823,7 @@
         <v>438</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>2073</v>
+        <v>2089</v>
       </c>
       <c r="G21" s="10">
         <v>21.8</v>
@@ -23497,12 +23833,12 @@
         <v>27</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>2092</v>
+        <v>2108</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>61</v>
@@ -23517,7 +23853,7 @@
         <v>451</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>2070</v>
+        <v>2086</v>
       </c>
       <c r="G22" s="8">
         <v>22</v>
@@ -23527,12 +23863,12 @@
         <v>27</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>2093</v>
+        <v>2109</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>61</v>
@@ -23547,7 +23883,7 @@
         <v>463</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>2073</v>
+        <v>2089</v>
       </c>
       <c r="G23" s="8">
         <v>23</v>
@@ -23557,12 +23893,12 @@
         <v>27</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>2094</v>
+        <v>2110</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>61</v>
@@ -23577,7 +23913,7 @@
         <v>475</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>2070</v>
+        <v>2086</v>
       </c>
       <c r="G24" s="10">
         <v>20.9</v>
@@ -23587,12 +23923,12 @@
         <v>27</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>2095</v>
+        <v>2111</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>61</v>
@@ -23607,7 +23943,7 @@
         <v>487</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>2073</v>
+        <v>2089</v>
       </c>
       <c r="G25" s="8">
         <v>22</v>
@@ -23617,12 +23953,12 @@
         <v>27</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>2096</v>
+        <v>2112</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>61</v>
@@ -23637,7 +23973,7 @@
         <v>499</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>2070</v>
+        <v>2086</v>
       </c>
       <c r="G26" s="10">
         <v>21.2</v>
@@ -23647,12 +23983,12 @@
         <v>27</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>2097</v>
+        <v>2113</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>61</v>
@@ -23667,7 +24003,7 @@
         <v>511</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>2073</v>
+        <v>2089</v>
       </c>
       <c r="G27" s="10">
         <v>21.8</v>
@@ -23677,12 +24013,12 @@
         <v>27</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>2098</v>
+        <v>2114</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>61</v>
@@ -23697,7 +24033,7 @@
         <v>523</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>2070</v>
+        <v>2086</v>
       </c>
       <c r="G28" s="10">
         <v>21.1</v>
@@ -23707,12 +24043,12 @@
         <v>27</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>2099</v>
+        <v>2115</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>61</v>
@@ -23727,7 +24063,7 @@
         <v>535</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>2073</v>
+        <v>2089</v>
       </c>
       <c r="G29" s="10">
         <v>21.8</v>
@@ -23737,12 +24073,12 @@
         <v>27</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>2100</v>
+        <v>2116</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>61</v>
@@ -23757,7 +24093,7 @@
         <v>547</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>2070</v>
+        <v>2086</v>
       </c>
       <c r="G30" s="10">
         <v>20.9</v>
@@ -23767,12 +24103,12 @@
         <v>27</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>2101</v>
+        <v>2117</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>61</v>
@@ -23787,7 +24123,7 @@
         <v>559</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>2073</v>
+        <v>2089</v>
       </c>
       <c r="G31" s="10">
         <v>21.7</v>
@@ -23797,12 +24133,12 @@
         <v>27</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>2102</v>
+        <v>2118</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>61</v>
@@ -23817,7 +24153,7 @@
         <v>571</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>2070</v>
+        <v>2086</v>
       </c>
       <c r="G32" s="8">
         <v>21</v>
@@ -23827,12 +24163,12 @@
         <v>27</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>2103</v>
+        <v>2119</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>61</v>
@@ -23847,7 +24183,7 @@
         <v>583</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>2073</v>
+        <v>2089</v>
       </c>
       <c r="G33" s="10">
         <v>21.9</v>
@@ -23857,12 +24193,12 @@
         <v>27</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>2104</v>
+        <v>2120</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>61</v>
@@ -23877,7 +24213,7 @@
         <v>595</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>2070</v>
+        <v>2086</v>
       </c>
       <c r="G34" s="10">
         <v>20.9</v>
@@ -23887,12 +24223,12 @@
         <v>27</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>2105</v>
+        <v>2121</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>61</v>
@@ -23907,7 +24243,7 @@
         <v>607</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>2073</v>
+        <v>2089</v>
       </c>
       <c r="G35" s="10">
         <v>21.9</v>
@@ -23917,12 +24253,12 @@
         <v>27</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>2106</v>
+        <v>2122</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>61</v>
@@ -23937,7 +24273,7 @@
         <v>619</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>2070</v>
+        <v>2086</v>
       </c>
       <c r="G36" s="10">
         <v>20.7</v>
@@ -23947,12 +24283,12 @@
         <v>27</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>2107</v>
+        <v>2123</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>61</v>
@@ -23967,7 +24303,7 @@
         <v>631</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>2073</v>
+        <v>2089</v>
       </c>
       <c r="G37" s="10">
         <v>21.8</v>
@@ -23977,12 +24313,12 @@
         <v>27</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>2108</v>
+        <v>2124</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>61</v>
@@ -23997,7 +24333,7 @@
         <v>643</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>2070</v>
+        <v>2086</v>
       </c>
       <c r="G38" s="10">
         <v>22.6</v>
@@ -24007,12 +24343,12 @@
         <v>27</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>2109</v>
+        <v>2125</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>61</v>
@@ -24027,7 +24363,7 @@
         <v>655</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>2073</v>
+        <v>2089</v>
       </c>
       <c r="G39" s="10">
         <v>23.2</v>
@@ -24037,12 +24373,12 @@
         <v>27</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>2110</v>
+        <v>2126</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>61</v>
@@ -24057,7 +24393,7 @@
         <v>667</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>2070</v>
+        <v>2086</v>
       </c>
       <c r="G40" s="10">
         <v>22.3</v>
@@ -24067,12 +24403,12 @@
         <v>27</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>2111</v>
+        <v>2127</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>61</v>
@@ -24087,7 +24423,7 @@
         <v>679</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>2073</v>
+        <v>2089</v>
       </c>
       <c r="G41" s="8">
         <v>23</v>
@@ -24097,12 +24433,12 @@
         <v>27</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>2112</v>
+        <v>2128</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>61</v>
@@ -24117,7 +24453,7 @@
         <v>691</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>2070</v>
+        <v>2086</v>
       </c>
       <c r="G42" s="10">
         <v>22.3</v>
@@ -24127,12 +24463,12 @@
         <v>27</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>2113</v>
+        <v>2129</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>61</v>
@@ -24147,7 +24483,7 @@
         <v>703</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>2073</v>
+        <v>2089</v>
       </c>
       <c r="G43" s="10">
         <v>23.1</v>
@@ -24157,12 +24493,12 @@
         <v>27</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>2114</v>
+        <v>2130</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>61</v>
@@ -24177,7 +24513,7 @@
         <v>715</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>2070</v>
+        <v>2086</v>
       </c>
       <c r="G44" s="10">
         <v>22.1</v>
@@ -24187,12 +24523,12 @@
         <v>27</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>2115</v>
+        <v>2131</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>61</v>
@@ -24207,7 +24543,7 @@
         <v>727</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>2073</v>
+        <v>2089</v>
       </c>
       <c r="G45" s="8">
         <v>23</v>
@@ -24217,12 +24553,12 @@
         <v>27</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>2116</v>
+        <v>2132</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>61</v>
@@ -24237,7 +24573,7 @@
         <v>739</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>2070</v>
+        <v>2086</v>
       </c>
       <c r="G46" s="8">
         <v>22</v>
@@ -24247,12 +24583,12 @@
         <v>27</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>2117</v>
+        <v>2133</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>61</v>
@@ -24267,7 +24603,7 @@
         <v>751</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>2073</v>
+        <v>2089</v>
       </c>
       <c r="G47" s="8">
         <v>23</v>
@@ -24277,12 +24613,12 @@
         <v>27</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>2118</v>
+        <v>2134</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>61</v>
@@ -24297,7 +24633,7 @@
         <v>763</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>2070</v>
+        <v>2086</v>
       </c>
       <c r="G48" s="8">
         <v>22</v>
@@ -24307,12 +24643,12 @@
         <v>27</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>2119</v>
+        <v>2135</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>61</v>
@@ -24327,7 +24663,7 @@
         <v>775</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>2073</v>
+        <v>2089</v>
       </c>
       <c r="G49" s="10">
         <v>23.1</v>
@@ -24337,12 +24673,12 @@
         <v>27</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>2120</v>
+        <v>2136</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>61</v>
@@ -24357,7 +24693,7 @@
         <v>204</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G50" s="10">
         <v>17.7</v>
@@ -24369,12 +24705,12 @@
         <v>20</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>2122</v>
+        <v>2138</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>61</v>
@@ -24389,7 +24725,7 @@
         <v>216</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G51" s="10">
         <v>17.8</v>
@@ -24401,12 +24737,12 @@
         <v>20</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>2123</v>
+        <v>2139</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>61</v>
@@ -24421,7 +24757,7 @@
         <v>229</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G52" s="10">
         <v>17.9</v>
@@ -24433,12 +24769,12 @@
         <v>20</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>2124</v>
+        <v>2140</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>61</v>
@@ -24453,7 +24789,7 @@
         <v>241</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G53" s="8">
         <v>18</v>
@@ -24465,12 +24801,12 @@
         <v>20</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>2125</v>
+        <v>2141</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>61</v>
@@ -24485,7 +24821,7 @@
         <v>254</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G54" s="10">
         <v>18.1</v>
@@ -24497,12 +24833,12 @@
         <v>20</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>2126</v>
+        <v>2142</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>61</v>
@@ -24517,7 +24853,7 @@
         <v>266</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G55" s="10">
         <v>18.2</v>
@@ -24529,12 +24865,12 @@
         <v>20</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>2127</v>
+        <v>2143</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>61</v>
@@ -24549,7 +24885,7 @@
         <v>280</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G56" s="10">
         <v>18.3</v>
@@ -24561,12 +24897,12 @@
         <v>20</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>2128</v>
+        <v>2144</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>61</v>
@@ -24581,7 +24917,7 @@
         <v>292</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G57" s="10">
         <v>18.4</v>
@@ -24593,12 +24929,12 @@
         <v>20</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>2129</v>
+        <v>2145</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>61</v>
@@ -24613,7 +24949,7 @@
         <v>305</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G58" s="10">
         <v>17.6</v>
@@ -24625,12 +24961,12 @@
         <v>20</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>2130</v>
+        <v>2146</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>61</v>
@@ -24645,7 +24981,7 @@
         <v>317</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G59" s="10">
         <v>17.7</v>
@@ -24657,12 +24993,12 @@
         <v>20</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>2131</v>
+        <v>2147</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>61</v>
@@ -24677,7 +25013,7 @@
         <v>330</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G60" s="10">
         <v>17.8</v>
@@ -24689,12 +25025,12 @@
         <v>20</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>2132</v>
+        <v>2148</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>61</v>
@@ -24709,7 +25045,7 @@
         <v>342</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G61" s="10">
         <v>17.9</v>
@@ -24721,12 +25057,12 @@
         <v>20</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>2133</v>
+        <v>2149</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>61</v>
@@ -24741,7 +25077,7 @@
         <v>354</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G62" s="8">
         <v>18</v>
@@ -24753,12 +25089,12 @@
         <v>20</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>2134</v>
+        <v>2150</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>61</v>
@@ -24773,7 +25109,7 @@
         <v>366</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G63" s="10">
         <v>18.1</v>
@@ -24785,12 +25121,12 @@
         <v>20</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>2135</v>
+        <v>2151</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>61</v>
@@ -24805,7 +25141,7 @@
         <v>378</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G64" s="10">
         <v>18.2</v>
@@ -24817,12 +25153,12 @@
         <v>20</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>2136</v>
+        <v>2152</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>61</v>
@@ -24837,7 +25173,7 @@
         <v>390</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G65" s="10">
         <v>18.3</v>
@@ -24849,12 +25185,12 @@
         <v>20</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>2137</v>
+        <v>2153</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>61</v>
@@ -24869,7 +25205,7 @@
         <v>402</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G66" s="10">
         <v>18.4</v>
@@ -24881,12 +25217,12 @@
         <v>20</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>2138</v>
+        <v>2154</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>61</v>
@@ -24901,7 +25237,7 @@
         <v>414</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G67" s="10">
         <v>17.6</v>
@@ -24913,12 +25249,12 @@
         <v>20</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>2139</v>
+        <v>2155</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>61</v>
@@ -24933,7 +25269,7 @@
         <v>426</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G68" s="10">
         <v>17.7</v>
@@ -24945,12 +25281,12 @@
         <v>20</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>2140</v>
+        <v>2156</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>61</v>
@@ -24965,7 +25301,7 @@
         <v>438</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G69" s="10">
         <v>17.8</v>
@@ -24977,12 +25313,12 @@
         <v>20</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>2141</v>
+        <v>2157</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>61</v>
@@ -24997,7 +25333,7 @@
         <v>451</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G70" s="10">
         <v>20.1</v>
@@ -25009,12 +25345,12 @@
         <v>20</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>2142</v>
+        <v>2158</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>61</v>
@@ -25029,7 +25365,7 @@
         <v>463</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G71" s="8">
         <v>18</v>
@@ -25041,12 +25377,12 @@
         <v>20</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>2143</v>
+        <v>2159</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>61</v>
@@ -25061,7 +25397,7 @@
         <v>475</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G72" s="10">
         <v>18.1</v>
@@ -25073,12 +25409,12 @@
         <v>20</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>2144</v>
+        <v>2160</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>61</v>
@@ -25093,7 +25429,7 @@
         <v>487</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G73" s="10">
         <v>18.2</v>
@@ -25105,12 +25441,12 @@
         <v>20</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>2145</v>
+        <v>2161</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>61</v>
@@ -25125,7 +25461,7 @@
         <v>499</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G74" s="10">
         <v>18.3</v>
@@ -25137,12 +25473,12 @@
         <v>20</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>2146</v>
+        <v>2162</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>61</v>
@@ -25157,7 +25493,7 @@
         <v>511</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G75" s="10">
         <v>18.4</v>
@@ -25169,12 +25505,12 @@
         <v>20</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>2147</v>
+        <v>2163</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>61</v>
@@ -25189,7 +25525,7 @@
         <v>523</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G76" s="10">
         <v>17.6</v>
@@ -25201,12 +25537,12 @@
         <v>20</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>2148</v>
+        <v>2164</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>61</v>
@@ -25221,7 +25557,7 @@
         <v>535</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G77" s="10">
         <v>17.7</v>
@@ -25233,12 +25569,12 @@
         <v>20</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>2149</v>
+        <v>2165</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>61</v>
@@ -25253,7 +25589,7 @@
         <v>547</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G78" s="10">
         <v>17.8</v>
@@ -25265,12 +25601,12 @@
         <v>20</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>2150</v>
+        <v>2166</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>61</v>
@@ -25285,7 +25621,7 @@
         <v>559</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G79" s="10">
         <v>17.9</v>
@@ -25297,12 +25633,12 @@
         <v>20</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>2151</v>
+        <v>2167</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>61</v>
@@ -25317,7 +25653,7 @@
         <v>571</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G80" s="8">
         <v>18</v>
@@ -25329,12 +25665,12 @@
         <v>20</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>2152</v>
+        <v>2168</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>61</v>
@@ -25349,7 +25685,7 @@
         <v>583</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G81" s="10">
         <v>18.1</v>
@@ -25361,12 +25697,12 @@
         <v>20</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>2153</v>
+        <v>2169</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>61</v>
@@ -25381,7 +25717,7 @@
         <v>595</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G82" s="10">
         <v>18.2</v>
@@ -25393,12 +25729,12 @@
         <v>20</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>2154</v>
+        <v>2170</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>61</v>
@@ -25413,7 +25749,7 @@
         <v>607</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G83" s="10">
         <v>18.3</v>
@@ -25425,12 +25761,12 @@
         <v>20</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>2155</v>
+        <v>2171</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>61</v>
@@ -25445,7 +25781,7 @@
         <v>619</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G84" s="10">
         <v>18.4</v>
@@ -25457,12 +25793,12 @@
         <v>20</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>2156</v>
+        <v>2172</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>61</v>
@@ -25477,7 +25813,7 @@
         <v>631</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G85" s="10">
         <v>17.6</v>
@@ -25489,12 +25825,12 @@
         <v>20</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>2157</v>
+        <v>2173</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>61</v>
@@ -25509,7 +25845,7 @@
         <v>643</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G86" s="10">
         <v>17.7</v>
@@ -25521,12 +25857,12 @@
         <v>20</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>2158</v>
+        <v>2174</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>61</v>
@@ -25541,7 +25877,7 @@
         <v>655</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G87" s="10">
         <v>17.8</v>
@@ -25553,12 +25889,12 @@
         <v>20</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>2159</v>
+        <v>2175</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>61</v>
@@ -25573,7 +25909,7 @@
         <v>667</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G88" s="10">
         <v>17.9</v>
@@ -25585,12 +25921,12 @@
         <v>20</v>
       </c>
       <c r="J88" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>2160</v>
+        <v>2176</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>61</v>
@@ -25605,7 +25941,7 @@
         <v>679</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G89" s="8">
         <v>18</v>
@@ -25617,12 +25953,12 @@
         <v>20</v>
       </c>
       <c r="J89" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>2161</v>
+        <v>2177</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>61</v>
@@ -25637,7 +25973,7 @@
         <v>691</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G90" s="10">
         <v>18.1</v>
@@ -25649,12 +25985,12 @@
         <v>20</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
-        <v>2162</v>
+        <v>2178</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>61</v>
@@ -25669,7 +26005,7 @@
         <v>703</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G91" s="10">
         <v>18.2</v>
@@ -25681,12 +26017,12 @@
         <v>20</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>2163</v>
+        <v>2179</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>61</v>
@@ -25701,7 +26037,7 @@
         <v>715</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G92" s="10">
         <v>18.3</v>
@@ -25713,12 +26049,12 @@
         <v>20</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
-        <v>2164</v>
+        <v>2180</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>61</v>
@@ -25733,7 +26069,7 @@
         <v>727</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G93" s="10">
         <v>18.4</v>
@@ -25745,12 +26081,12 @@
         <v>20</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>2165</v>
+        <v>2181</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>61</v>
@@ -25765,7 +26101,7 @@
         <v>739</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G94" s="10">
         <v>17.6</v>
@@ -25777,12 +26113,12 @@
         <v>20</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>2166</v>
+        <v>2182</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>61</v>
@@ -25797,7 +26133,7 @@
         <v>751</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G95" s="10">
         <v>17.7</v>
@@ -25809,12 +26145,12 @@
         <v>20</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>2167</v>
+        <v>2183</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>61</v>
@@ -25829,7 +26165,7 @@
         <v>763</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G96" s="10">
         <v>17.8</v>
@@ -25841,12 +26177,12 @@
         <v>20</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
-        <v>2168</v>
+        <v>2184</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>61</v>
@@ -25861,7 +26197,7 @@
         <v>775</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>2121</v>
+        <v>2137</v>
       </c>
       <c r="G97" s="10">
         <v>17.9</v>
@@ -25873,17 +26209,17 @@
         <v>20</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>2071</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="9" t="s">
-        <v>2169</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="9" t="s">
-        <v>2170</v>
+        <v>2186</v>
       </c>
     </row>
   </sheetData>

--- a/nexus_demo_dataset.xlsx
+++ b/nexus_demo_dataset.xlsx
@@ -5870,7 +5870,7 @@
     <t>outage</t>
   </si>
   <si>
-    <t>resistance trending|capacity fade|Battery batch</t>
+    <t>resistance trending|internal resistance|capacity fade|Battery batch</t>
   </si>
   <si>
     <t>Confirm the string resistance trend against the last discharge test</t>
@@ -5894,7 +5894,7 @@
     <t>Supply air above setpoint</t>
   </si>
   <si>
-    <t>Supply air temp|Actuator seized</t>
+    <t>Supply air temp|actuator</t>
   </si>
   <si>
     <t>Check chilled-water valve actuator response at the unit</t>

--- a/nexus_demo_dataset.xlsx
+++ b/nexus_demo_dataset.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9767" uniqueCount="2210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9778" uniqueCount="2211">
   <si>
     <t>Nexus Data Infrastructure - K-Nexus demo dataset</t>
   </si>
@@ -5789,6 +5789,9 @@
     <t>uptime_pct</t>
   </si>
   <si>
+    <t>2024-09</t>
+  </si>
+  <si>
     <t>2024-10</t>
   </si>
   <si>
@@ -5837,7 +5840,7 @@
     <t>COOLING EFFICIENCY DRIFT</t>
   </si>
   <si>
-    <t>24 months to September 2026.</t>
+    <t>25 months, September 2024 to September 2026. September 2026 is month to date at 29 September.</t>
   </si>
   <si>
     <t>MUM-1 PUE drifts upward from month 19 - 0.013 per month of cooling efficiency loss.</t>
@@ -10377,28 +10380,28 @@
         <v>1482</v>
       </c>
       <c r="C2" s="8">
-        <v>7452648</v>
+        <v>7591014</v>
       </c>
       <c r="D2" s="8">
-        <v>1639583</v>
+        <v>1670023</v>
       </c>
       <c r="E2" s="8">
-        <v>5813065</v>
+        <v>5920991</v>
       </c>
       <c r="F2" s="7">
         <v>8.5</v>
       </c>
       <c r="G2" s="7">
-        <v>633.5</v>
+        <v>645.2</v>
       </c>
       <c r="H2" s="7">
-        <v>1.575</v>
+        <v>1.568</v>
       </c>
       <c r="I2" s="7">
         <v>0.71</v>
       </c>
       <c r="J2" s="7">
-        <v>4127.3</v>
+        <v>4203.9</v>
       </c>
       <c r="K2" s="8">
         <v>0</v>
@@ -10412,19 +10415,19 @@
         <v>1483</v>
       </c>
       <c r="C3" s="8">
-        <v>6856400</v>
+        <v>6911192</v>
       </c>
       <c r="D3" s="8">
-        <v>1508408</v>
+        <v>1520462</v>
       </c>
       <c r="E3" s="8">
-        <v>5347992</v>
+        <v>5390730</v>
       </c>
       <c r="F3" s="7">
         <v>8.5</v>
       </c>
       <c r="G3" s="7">
-        <v>582.8</v>
+        <v>587.5</v>
       </c>
       <c r="H3" s="7">
         <v>1.568</v>
@@ -10433,7 +10436,7 @@
         <v>0.71</v>
       </c>
       <c r="J3" s="7">
-        <v>3797.1</v>
+        <v>3827.4</v>
       </c>
       <c r="K3" s="8">
         <v>0</v>
@@ -10447,28 +10450,28 @@
         <v>1484</v>
       </c>
       <c r="C4" s="8">
-        <v>7651677</v>
+        <v>7650677</v>
       </c>
       <c r="D4" s="8">
-        <v>1683369</v>
+        <v>1683149</v>
       </c>
       <c r="E4" s="8">
-        <v>5968308</v>
+        <v>5967528</v>
       </c>
       <c r="F4" s="7">
         <v>8.5</v>
       </c>
       <c r="G4" s="7">
-        <v>650.4</v>
+        <v>650.3</v>
       </c>
       <c r="H4" s="7">
-        <v>1.568</v>
+        <v>1.583</v>
       </c>
       <c r="I4" s="7">
         <v>0.71</v>
       </c>
       <c r="J4" s="7">
-        <v>4237.5</v>
+        <v>4236.9</v>
       </c>
       <c r="K4" s="8">
         <v>0</v>
@@ -10482,28 +10485,28 @@
         <v>1485</v>
       </c>
       <c r="C5" s="8">
-        <v>7403881</v>
+        <v>7664786</v>
       </c>
       <c r="D5" s="8">
-        <v>1628854</v>
+        <v>1686253</v>
       </c>
       <c r="E5" s="8">
-        <v>5775027</v>
+        <v>5978533</v>
       </c>
       <c r="F5" s="7">
         <v>8.5</v>
       </c>
       <c r="G5" s="7">
-        <v>629.3</v>
+        <v>651.5</v>
       </c>
       <c r="H5" s="7">
-        <v>1.583</v>
+        <v>1.632</v>
       </c>
       <c r="I5" s="7">
         <v>0.71</v>
       </c>
       <c r="J5" s="7">
-        <v>4100.3</v>
+        <v>4244.8</v>
       </c>
       <c r="K5" s="8">
         <v>0</v>
@@ -10517,28 +10520,28 @@
         <v>1486</v>
       </c>
       <c r="C6" s="8">
-        <v>7920279</v>
+        <v>8065369</v>
       </c>
       <c r="D6" s="8">
-        <v>1742461</v>
+        <v>1774381</v>
       </c>
       <c r="E6" s="8">
-        <v>6177818</v>
+        <v>6290988</v>
       </c>
       <c r="F6" s="7">
         <v>8.5</v>
       </c>
       <c r="G6" s="7">
-        <v>673.2</v>
+        <v>685.6</v>
       </c>
       <c r="H6" s="7">
-        <v>1.632</v>
+        <v>1.645</v>
       </c>
       <c r="I6" s="7">
         <v>0.71</v>
       </c>
       <c r="J6" s="7">
-        <v>4386.3</v>
+        <v>4466.6</v>
       </c>
       <c r="K6" s="8">
         <v>0</v>
@@ -10552,28 +10555,28 @@
         <v>1487</v>
       </c>
       <c r="C7" s="8">
-        <v>7805196</v>
+        <v>7937321</v>
       </c>
       <c r="D7" s="8">
-        <v>1717143</v>
+        <v>1746211</v>
       </c>
       <c r="E7" s="8">
-        <v>6088053</v>
+        <v>6191110</v>
       </c>
       <c r="F7" s="7">
         <v>8.5</v>
       </c>
       <c r="G7" s="7">
-        <v>663.4</v>
+        <v>674.7</v>
       </c>
       <c r="H7" s="7">
-        <v>1.645</v>
+        <v>1.661</v>
       </c>
       <c r="I7" s="7">
         <v>0.71</v>
       </c>
       <c r="J7" s="7">
-        <v>4322.5</v>
+        <v>4395.7</v>
       </c>
       <c r="K7" s="8">
         <v>0</v>
@@ -10587,28 +10590,28 @@
         <v>1488</v>
       </c>
       <c r="C8" s="8">
-        <v>8201898</v>
+        <v>8251833</v>
       </c>
       <c r="D8" s="8">
-        <v>1804418</v>
+        <v>1815403</v>
       </c>
       <c r="E8" s="8">
-        <v>6397480</v>
+        <v>6436430</v>
       </c>
       <c r="F8" s="7">
         <v>8.5</v>
       </c>
       <c r="G8" s="7">
-        <v>697.2</v>
+        <v>701.4</v>
       </c>
       <c r="H8" s="7">
-        <v>1.661</v>
+        <v>1.649</v>
       </c>
       <c r="I8" s="7">
         <v>0.71</v>
       </c>
       <c r="J8" s="7">
-        <v>4542.2</v>
+        <v>4569.9</v>
       </c>
       <c r="K8" s="8">
         <v>0</v>
@@ -10622,28 +10625,28 @@
         <v>1489</v>
       </c>
       <c r="C9" s="8">
-        <v>8251833</v>
+        <v>8512742</v>
       </c>
       <c r="D9" s="8">
-        <v>1815403</v>
+        <v>1872803</v>
       </c>
       <c r="E9" s="8">
-        <v>6436430</v>
+        <v>6639939</v>
       </c>
       <c r="F9" s="7">
         <v>8.5</v>
       </c>
       <c r="G9" s="7">
-        <v>701.4</v>
+        <v>723.6</v>
       </c>
       <c r="H9" s="7">
-        <v>1.649</v>
+        <v>1.658</v>
       </c>
       <c r="I9" s="7">
         <v>0.71</v>
       </c>
       <c r="J9" s="7">
-        <v>4569.9</v>
+        <v>4714.4</v>
       </c>
       <c r="K9" s="8">
         <v>0</v>
@@ -10657,28 +10660,28 @@
         <v>1490</v>
       </c>
       <c r="C10" s="8">
-        <v>8238138</v>
+        <v>8268005</v>
       </c>
       <c r="D10" s="8">
-        <v>1812390</v>
+        <v>1818961</v>
       </c>
       <c r="E10" s="8">
-        <v>6425748</v>
+        <v>6449044</v>
       </c>
       <c r="F10" s="7">
         <v>8.5</v>
       </c>
       <c r="G10" s="7">
-        <v>700.2</v>
+        <v>702.8</v>
       </c>
       <c r="H10" s="7">
-        <v>1.658</v>
+        <v>1.644</v>
       </c>
       <c r="I10" s="7">
         <v>0.71</v>
       </c>
       <c r="J10" s="7">
-        <v>4562.3</v>
+        <v>4578.8</v>
       </c>
       <c r="K10" s="8">
         <v>0</v>
@@ -10692,28 +10695,28 @@
         <v>1482</v>
       </c>
       <c r="C11" s="8">
-        <v>5985294</v>
+        <v>6130614</v>
       </c>
       <c r="D11" s="8">
-        <v>837941</v>
+        <v>858286</v>
       </c>
       <c r="E11" s="8">
-        <v>5147353</v>
+        <v>5272328</v>
       </c>
       <c r="F11" s="7">
         <v>8.5</v>
       </c>
       <c r="G11" s="7">
-        <v>508.7</v>
+        <v>521.1</v>
       </c>
       <c r="H11" s="7">
-        <v>1.75</v>
+        <v>1.748</v>
       </c>
       <c r="I11" s="7">
         <v>0.71</v>
       </c>
       <c r="J11" s="7">
-        <v>3654.6</v>
+        <v>3743.4</v>
       </c>
       <c r="K11" s="8">
         <v>0</v>
@@ -10727,28 +10730,28 @@
         <v>1483</v>
       </c>
       <c r="C12" s="8">
-        <v>5537328</v>
+        <v>5592958</v>
       </c>
       <c r="D12" s="8">
-        <v>775226</v>
+        <v>783014</v>
       </c>
       <c r="E12" s="8">
-        <v>4762102</v>
+        <v>4809944</v>
       </c>
       <c r="F12" s="7">
         <v>8.5</v>
       </c>
       <c r="G12" s="7">
-        <v>470.7</v>
+        <v>475.4</v>
       </c>
       <c r="H12" s="7">
-        <v>1.748</v>
+        <v>1.739</v>
       </c>
       <c r="I12" s="7">
         <v>0.71</v>
       </c>
       <c r="J12" s="7">
-        <v>3381.1</v>
+        <v>3415.1</v>
       </c>
       <c r="K12" s="8">
         <v>0</v>
@@ -10762,28 +10765,28 @@
         <v>1484</v>
       </c>
       <c r="C13" s="8">
-        <v>6192203</v>
+        <v>6239851</v>
       </c>
       <c r="D13" s="8">
-        <v>866908</v>
+        <v>873579</v>
       </c>
       <c r="E13" s="8">
-        <v>5325295</v>
+        <v>5366272</v>
       </c>
       <c r="F13" s="7">
         <v>8.5</v>
       </c>
       <c r="G13" s="7">
-        <v>526.3</v>
+        <v>530.4</v>
       </c>
       <c r="H13" s="7">
-        <v>1.739</v>
+        <v>1.744</v>
       </c>
       <c r="I13" s="7">
         <v>0.71</v>
       </c>
       <c r="J13" s="7">
-        <v>3781</v>
+        <v>3810.1</v>
       </c>
       <c r="K13" s="8">
         <v>0</v>
@@ -10797,28 +10800,28 @@
         <v>1485</v>
       </c>
       <c r="C14" s="8">
-        <v>6038565</v>
+        <v>6210789</v>
       </c>
       <c r="D14" s="8">
-        <v>845399</v>
+        <v>869510</v>
       </c>
       <c r="E14" s="8">
-        <v>5193166</v>
+        <v>5341279</v>
       </c>
       <c r="F14" s="7">
         <v>8.5</v>
       </c>
       <c r="G14" s="7">
-        <v>513.3</v>
+        <v>527.9</v>
       </c>
       <c r="H14" s="7">
-        <v>1.744</v>
+        <v>1.772</v>
       </c>
       <c r="I14" s="7">
         <v>0.71</v>
       </c>
       <c r="J14" s="7">
-        <v>3687.1</v>
+        <v>3792.3</v>
       </c>
       <c r="K14" s="8">
         <v>0</v>
@@ -10832,28 +10835,28 @@
         <v>1486</v>
       </c>
       <c r="C15" s="8">
-        <v>6417815</v>
+        <v>6401184</v>
       </c>
       <c r="D15" s="8">
-        <v>898494</v>
+        <v>896166</v>
       </c>
       <c r="E15" s="8">
-        <v>5519321</v>
+        <v>5505018</v>
       </c>
       <c r="F15" s="7">
         <v>8.5</v>
       </c>
       <c r="G15" s="7">
-        <v>545.5</v>
+        <v>544.1</v>
       </c>
       <c r="H15" s="7">
-        <v>1.772</v>
+        <v>1.778</v>
       </c>
       <c r="I15" s="7">
         <v>0.71</v>
       </c>
       <c r="J15" s="7">
-        <v>3918.7</v>
+        <v>3908.6</v>
       </c>
       <c r="K15" s="8">
         <v>0</v>
@@ -10867,28 +10870,28 @@
         <v>1487</v>
       </c>
       <c r="C16" s="8">
-        <v>6194694</v>
+        <v>6282063</v>
       </c>
       <c r="D16" s="8">
-        <v>867257</v>
+        <v>879489</v>
       </c>
       <c r="E16" s="8">
-        <v>5327437</v>
+        <v>5402574</v>
       </c>
       <c r="F16" s="7">
         <v>8.5</v>
       </c>
       <c r="G16" s="7">
-        <v>526.5</v>
+        <v>534</v>
       </c>
       <c r="H16" s="7">
-        <v>1.778</v>
+        <v>1.763</v>
       </c>
       <c r="I16" s="7">
         <v>0.71</v>
       </c>
       <c r="J16" s="7">
-        <v>3782.5</v>
+        <v>3835.8</v>
       </c>
       <c r="K16" s="8">
         <v>0</v>
@@ -10902,28 +10905,28 @@
         <v>1488</v>
       </c>
       <c r="C17" s="8">
-        <v>6491465</v>
+        <v>6466821</v>
       </c>
       <c r="D17" s="8">
-        <v>908805</v>
+        <v>905355</v>
       </c>
       <c r="E17" s="8">
-        <v>5582660</v>
+        <v>5561466</v>
       </c>
       <c r="F17" s="7">
         <v>8.5</v>
       </c>
       <c r="G17" s="7">
-        <v>551.8</v>
+        <v>549.7</v>
       </c>
       <c r="H17" s="7">
-        <v>1.763</v>
+        <v>1.751</v>
       </c>
       <c r="I17" s="7">
         <v>0.71</v>
       </c>
       <c r="J17" s="7">
-        <v>3963.7</v>
+        <v>3948.6</v>
       </c>
       <c r="K17" s="8">
         <v>0</v>
@@ -10937,28 +10940,28 @@
         <v>1489</v>
       </c>
       <c r="C18" s="8">
-        <v>6466821</v>
+        <v>6498282</v>
       </c>
       <c r="D18" s="8">
-        <v>905355</v>
+        <v>909759</v>
       </c>
       <c r="E18" s="8">
-        <v>5561466</v>
+        <v>5588523</v>
       </c>
       <c r="F18" s="7">
         <v>8.5</v>
       </c>
       <c r="G18" s="7">
-        <v>549.7</v>
+        <v>552.4</v>
       </c>
       <c r="H18" s="7">
-        <v>1.751</v>
+        <v>1.75</v>
       </c>
       <c r="I18" s="7">
         <v>0.71</v>
       </c>
       <c r="J18" s="7">
-        <v>3948.6</v>
+        <v>3967.9</v>
       </c>
       <c r="K18" s="8">
         <v>0</v>
@@ -10972,28 +10975,28 @@
         <v>1490</v>
       </c>
       <c r="C19" s="8">
-        <v>6288660</v>
+        <v>6280978</v>
       </c>
       <c r="D19" s="8">
-        <v>880412</v>
+        <v>879337</v>
       </c>
       <c r="E19" s="8">
-        <v>5408248</v>
+        <v>5401641</v>
       </c>
       <c r="F19" s="7">
         <v>8.5</v>
       </c>
       <c r="G19" s="7">
-        <v>534.5</v>
+        <v>533.9</v>
       </c>
       <c r="H19" s="7">
-        <v>1.75</v>
+        <v>1.735</v>
       </c>
       <c r="I19" s="7">
         <v>0.71</v>
       </c>
       <c r="J19" s="7">
-        <v>3839.9</v>
+        <v>3835.2</v>
       </c>
       <c r="K19" s="8">
         <v>0</v>
@@ -11007,28 +11010,28 @@
         <v>1482</v>
       </c>
       <c r="C20" s="8">
-        <v>6233235</v>
+        <v>6259615</v>
       </c>
       <c r="D20" s="8">
-        <v>1932303</v>
+        <v>1940481</v>
       </c>
       <c r="E20" s="8">
-        <v>4300932</v>
+        <v>4319134</v>
       </c>
       <c r="F20" s="7">
         <v>7.9</v>
       </c>
       <c r="G20" s="7">
-        <v>492.4</v>
+        <v>494.5</v>
       </c>
       <c r="H20" s="7">
-        <v>1.618</v>
+        <v>1.609</v>
       </c>
       <c r="I20" s="7">
         <v>0.71</v>
       </c>
       <c r="J20" s="7">
-        <v>3053.7</v>
+        <v>3066.6</v>
       </c>
       <c r="K20" s="8">
         <v>0</v>
@@ -11042,28 +11045,28 @@
         <v>1483</v>
       </c>
       <c r="C21" s="8">
-        <v>5653846</v>
+        <v>5577935</v>
       </c>
       <c r="D21" s="8">
-        <v>1752692</v>
+        <v>1729160</v>
       </c>
       <c r="E21" s="8">
-        <v>3901154</v>
+        <v>3848775</v>
       </c>
       <c r="F21" s="7">
         <v>7.9</v>
       </c>
       <c r="G21" s="7">
-        <v>446.7</v>
+        <v>440.7</v>
       </c>
       <c r="H21" s="7">
-        <v>1.609</v>
+        <v>1.613</v>
       </c>
       <c r="I21" s="7">
         <v>0.71</v>
       </c>
       <c r="J21" s="7">
-        <v>2769.8</v>
+        <v>2732.6</v>
       </c>
       <c r="K21" s="8">
         <v>0</v>
@@ -11077,28 +11080,28 @@
         <v>1484</v>
       </c>
       <c r="C22" s="8">
-        <v>6175571</v>
+        <v>6400037</v>
       </c>
       <c r="D22" s="8">
-        <v>1914427</v>
+        <v>1984011</v>
       </c>
       <c r="E22" s="8">
-        <v>4261144</v>
+        <v>4416026</v>
       </c>
       <c r="F22" s="7">
         <v>7.9</v>
       </c>
       <c r="G22" s="7">
-        <v>487.9</v>
+        <v>505.6</v>
       </c>
       <c r="H22" s="7">
-        <v>1.613</v>
+        <v>1.62</v>
       </c>
       <c r="I22" s="7">
         <v>0.71</v>
       </c>
       <c r="J22" s="7">
-        <v>3025.4</v>
+        <v>3135.4</v>
       </c>
       <c r="K22" s="8">
         <v>0</v>
@@ -11112,28 +11115,28 @@
         <v>1485</v>
       </c>
       <c r="C23" s="8">
-        <v>6193584</v>
+        <v>6358108</v>
       </c>
       <c r="D23" s="8">
-        <v>1920011</v>
+        <v>1971013</v>
       </c>
       <c r="E23" s="8">
-        <v>4273573</v>
+        <v>4387095</v>
       </c>
       <c r="F23" s="7">
         <v>7.9</v>
       </c>
       <c r="G23" s="7">
-        <v>489.3</v>
+        <v>502.3</v>
       </c>
       <c r="H23" s="7">
-        <v>1.62</v>
+        <v>1.654</v>
       </c>
       <c r="I23" s="7">
         <v>0.71</v>
       </c>
       <c r="J23" s="7">
-        <v>3034.2</v>
+        <v>3114.8</v>
       </c>
       <c r="K23" s="8">
         <v>0</v>
@@ -11147,28 +11150,28 @@
         <v>1486</v>
       </c>
       <c r="C24" s="8">
-        <v>6570045</v>
+        <v>6483960</v>
       </c>
       <c r="D24" s="8">
-        <v>2036714</v>
+        <v>2010028</v>
       </c>
       <c r="E24" s="8">
-        <v>4533331</v>
+        <v>4473932</v>
       </c>
       <c r="F24" s="7">
         <v>7.9</v>
       </c>
       <c r="G24" s="7">
-        <v>519</v>
+        <v>512.2</v>
       </c>
       <c r="H24" s="7">
-        <v>1.654</v>
+        <v>1.66</v>
       </c>
       <c r="I24" s="7">
         <v>0.71</v>
       </c>
       <c r="J24" s="7">
-        <v>3218.7</v>
+        <v>3176.5</v>
       </c>
       <c r="K24" s="8">
         <v>0</v>
@@ -11182,28 +11185,28 @@
         <v>1487</v>
       </c>
       <c r="C25" s="8">
-        <v>6274800</v>
+        <v>6366578</v>
       </c>
       <c r="D25" s="8">
-        <v>1945188</v>
+        <v>1973639</v>
       </c>
       <c r="E25" s="8">
-        <v>4329612</v>
+        <v>4392939</v>
       </c>
       <c r="F25" s="7">
         <v>7.9</v>
       </c>
       <c r="G25" s="7">
-        <v>495.7</v>
+        <v>503</v>
       </c>
       <c r="H25" s="7">
-        <v>1.66</v>
+        <v>1.659</v>
       </c>
       <c r="I25" s="7">
         <v>0.71</v>
       </c>
       <c r="J25" s="7">
-        <v>3074</v>
+        <v>3119</v>
       </c>
       <c r="K25" s="8">
         <v>0</v>
@@ -11217,28 +11220,28 @@
         <v>1488</v>
       </c>
       <c r="C26" s="8">
-        <v>6578798</v>
+        <v>6607506</v>
       </c>
       <c r="D26" s="8">
-        <v>2039427</v>
+        <v>2048327</v>
       </c>
       <c r="E26" s="8">
-        <v>4539371</v>
+        <v>4559179</v>
       </c>
       <c r="F26" s="7">
         <v>7.9</v>
       </c>
       <c r="G26" s="7">
-        <v>519.7</v>
+        <v>522</v>
       </c>
       <c r="H26" s="7">
-        <v>1.659</v>
+        <v>1.623</v>
       </c>
       <c r="I26" s="7">
         <v>0.71</v>
       </c>
       <c r="J26" s="7">
-        <v>3223</v>
+        <v>3237</v>
       </c>
       <c r="K26" s="8">
         <v>0</v>
@@ -11252,28 +11255,28 @@
         <v>1489</v>
       </c>
       <c r="C27" s="8">
-        <v>6607506</v>
+        <v>6589476</v>
       </c>
       <c r="D27" s="8">
-        <v>2048327</v>
+        <v>2042738</v>
       </c>
       <c r="E27" s="8">
-        <v>4559179</v>
+        <v>4546738</v>
       </c>
       <c r="F27" s="7">
         <v>7.9</v>
       </c>
       <c r="G27" s="7">
-        <v>522</v>
+        <v>520.6</v>
       </c>
       <c r="H27" s="7">
-        <v>1.623</v>
+        <v>1.626</v>
       </c>
       <c r="I27" s="7">
         <v>0.71</v>
       </c>
       <c r="J27" s="7">
-        <v>3237</v>
+        <v>3228.2</v>
       </c>
       <c r="K27" s="8">
         <v>0</v>
@@ -11287,28 +11290,28 @@
         <v>1490</v>
       </c>
       <c r="C28" s="8">
-        <v>6376912</v>
+        <v>6382098</v>
       </c>
       <c r="D28" s="8">
-        <v>1976843</v>
+        <v>1978450</v>
       </c>
       <c r="E28" s="8">
-        <v>4400069</v>
+        <v>4403648</v>
       </c>
       <c r="F28" s="7">
         <v>7.9</v>
       </c>
       <c r="G28" s="7">
-        <v>503.8</v>
+        <v>504.2</v>
       </c>
       <c r="H28" s="7">
-        <v>1.626</v>
+        <v>1.619</v>
       </c>
       <c r="I28" s="7">
         <v>0.71</v>
       </c>
       <c r="J28" s="7">
-        <v>3124</v>
+        <v>3126.6</v>
       </c>
       <c r="K28" s="8">
         <v>0</v>
@@ -11322,28 +11325,28 @@
         <v>1482</v>
       </c>
       <c r="C29" s="8">
-        <v>7147726</v>
+        <v>7132285</v>
       </c>
       <c r="D29" s="8">
-        <v>4860454</v>
+        <v>4849954</v>
       </c>
       <c r="E29" s="8">
-        <v>2287272</v>
+        <v>2282331</v>
       </c>
       <c r="F29" s="7">
         <v>7.2</v>
       </c>
       <c r="G29" s="7">
-        <v>514.6</v>
+        <v>513.5</v>
       </c>
       <c r="H29" s="7">
-        <v>1.331</v>
+        <v>1.332</v>
       </c>
       <c r="I29" s="7">
         <v>0.71</v>
       </c>
       <c r="J29" s="7">
-        <v>1624</v>
+        <v>1620.5</v>
       </c>
       <c r="K29" s="8">
         <v>0</v>
@@ -11357,28 +11360,28 @@
         <v>1483</v>
       </c>
       <c r="C30" s="8">
-        <v>6442063</v>
+        <v>6591927</v>
       </c>
       <c r="D30" s="8">
-        <v>4380603</v>
+        <v>4482510</v>
       </c>
       <c r="E30" s="8">
-        <v>2061460</v>
+        <v>2109417</v>
       </c>
       <c r="F30" s="7">
         <v>7.2</v>
       </c>
       <c r="G30" s="7">
-        <v>463.8</v>
+        <v>474.6</v>
       </c>
       <c r="H30" s="7">
-        <v>1.332</v>
+        <v>1.341</v>
       </c>
       <c r="I30" s="7">
         <v>0.71</v>
       </c>
       <c r="J30" s="7">
-        <v>1463.6</v>
+        <v>1497.7</v>
       </c>
       <c r="K30" s="8">
         <v>0</v>
@@ -11392,13 +11395,13 @@
         <v>1484</v>
       </c>
       <c r="C31" s="8">
-        <v>7298205</v>
+        <v>7298774</v>
       </c>
       <c r="D31" s="8">
-        <v>4962779</v>
+        <v>4963166</v>
       </c>
       <c r="E31" s="8">
-        <v>2335426</v>
+        <v>2335608</v>
       </c>
       <c r="F31" s="7">
         <v>7.2</v>
@@ -11407,13 +11410,13 @@
         <v>525.5</v>
       </c>
       <c r="H31" s="7">
-        <v>1.341</v>
+        <v>1.332</v>
       </c>
       <c r="I31" s="7">
         <v>0.71</v>
       </c>
       <c r="J31" s="7">
-        <v>1658.2</v>
+        <v>1658.3</v>
       </c>
       <c r="K31" s="8">
         <v>0</v>
@@ -11427,28 +11430,28 @@
         <v>1485</v>
       </c>
       <c r="C32" s="8">
-        <v>7063330</v>
+        <v>7360001</v>
       </c>
       <c r="D32" s="8">
-        <v>4803064</v>
+        <v>5004801</v>
       </c>
       <c r="E32" s="8">
-        <v>2260266</v>
+        <v>2355200</v>
       </c>
       <c r="F32" s="7">
         <v>7.2</v>
       </c>
       <c r="G32" s="7">
-        <v>508.6</v>
+        <v>529.9</v>
       </c>
       <c r="H32" s="7">
-        <v>1.332</v>
+        <v>1.384</v>
       </c>
       <c r="I32" s="7">
         <v>0.71</v>
       </c>
       <c r="J32" s="7">
-        <v>1604.8</v>
+        <v>1672.2</v>
       </c>
       <c r="K32" s="8">
         <v>0</v>
@@ -11462,28 +11465,28 @@
         <v>1486</v>
       </c>
       <c r="C33" s="8">
-        <v>7605335</v>
+        <v>7764982</v>
       </c>
       <c r="D33" s="8">
-        <v>5171628</v>
+        <v>5280188</v>
       </c>
       <c r="E33" s="8">
-        <v>2433707</v>
+        <v>2484794</v>
       </c>
       <c r="F33" s="7">
         <v>7.2</v>
       </c>
       <c r="G33" s="7">
-        <v>547.6</v>
+        <v>559.1</v>
       </c>
       <c r="H33" s="7">
-        <v>1.384</v>
+        <v>1.372</v>
       </c>
       <c r="I33" s="7">
         <v>0.71</v>
       </c>
       <c r="J33" s="7">
-        <v>1727.9</v>
+        <v>1764.2</v>
       </c>
       <c r="K33" s="8">
         <v>0</v>
@@ -11497,28 +11500,28 @@
         <v>1487</v>
       </c>
       <c r="C34" s="8">
-        <v>7514499</v>
+        <v>7522286</v>
       </c>
       <c r="D34" s="8">
-        <v>5109859</v>
+        <v>5115154</v>
       </c>
       <c r="E34" s="8">
-        <v>2404640</v>
+        <v>2407132</v>
       </c>
       <c r="F34" s="7">
         <v>7.2</v>
       </c>
       <c r="G34" s="7">
-        <v>541</v>
+        <v>541.6</v>
       </c>
       <c r="H34" s="7">
-        <v>1.372</v>
+        <v>1.37</v>
       </c>
       <c r="I34" s="7">
         <v>0.71</v>
       </c>
       <c r="J34" s="7">
-        <v>1707.3</v>
+        <v>1709.1</v>
       </c>
       <c r="K34" s="8">
         <v>0</v>
@@ -11532,28 +11535,28 @@
         <v>1488</v>
       </c>
       <c r="C35" s="8">
-        <v>7773029</v>
+        <v>7582110</v>
       </c>
       <c r="D35" s="8">
-        <v>5285660</v>
+        <v>5155835</v>
       </c>
       <c r="E35" s="8">
-        <v>2487369</v>
+        <v>2426275</v>
       </c>
       <c r="F35" s="7">
         <v>7.2</v>
       </c>
       <c r="G35" s="7">
-        <v>559.7</v>
+        <v>545.9</v>
       </c>
       <c r="H35" s="7">
-        <v>1.37</v>
+        <v>1.336</v>
       </c>
       <c r="I35" s="7">
         <v>0.71</v>
       </c>
       <c r="J35" s="7">
-        <v>1766</v>
+        <v>1722.7</v>
       </c>
       <c r="K35" s="8">
         <v>0</v>
@@ -11567,28 +11570,28 @@
         <v>1489</v>
       </c>
       <c r="C36" s="8">
-        <v>7582110</v>
+        <v>7587488</v>
       </c>
       <c r="D36" s="8">
-        <v>5155835</v>
+        <v>5159492</v>
       </c>
       <c r="E36" s="8">
-        <v>2426275</v>
+        <v>2427996</v>
       </c>
       <c r="F36" s="7">
         <v>7.2</v>
       </c>
       <c r="G36" s="7">
-        <v>545.9</v>
+        <v>546.3</v>
       </c>
       <c r="H36" s="7">
-        <v>1.336</v>
+        <v>1.338</v>
       </c>
       <c r="I36" s="7">
         <v>0.71</v>
       </c>
       <c r="J36" s="7">
-        <v>1722.7</v>
+        <v>1723.9</v>
       </c>
       <c r="K36" s="8">
         <v>0</v>
@@ -11602,28 +11605,28 @@
         <v>1490</v>
       </c>
       <c r="C37" s="8">
-        <v>7342730</v>
+        <v>7354148</v>
       </c>
       <c r="D37" s="8">
-        <v>4993056</v>
+        <v>5000821</v>
       </c>
       <c r="E37" s="8">
-        <v>2349674</v>
+        <v>2353327</v>
       </c>
       <c r="F37" s="7">
         <v>7.2</v>
       </c>
       <c r="G37" s="7">
-        <v>528.7</v>
+        <v>529.5</v>
       </c>
       <c r="H37" s="7">
-        <v>1.338</v>
+        <v>1.331</v>
       </c>
       <c r="I37" s="7">
         <v>0.71</v>
       </c>
       <c r="J37" s="7">
-        <v>1668.3</v>
+        <v>1670.9</v>
       </c>
       <c r="K37" s="8">
         <v>0</v>
@@ -11637,28 +11640,28 @@
         <v>1482</v>
       </c>
       <c r="C38" s="8">
-        <v>8829985</v>
+        <v>8919712</v>
       </c>
       <c r="D38" s="8">
-        <v>1677697</v>
+        <v>1694745</v>
       </c>
       <c r="E38" s="8">
-        <v>7152288</v>
+        <v>7224967</v>
       </c>
       <c r="F38" s="7">
         <v>8.15</v>
       </c>
       <c r="G38" s="7">
-        <v>719.6</v>
+        <v>727</v>
       </c>
       <c r="H38" s="7">
-        <v>1.669</v>
+        <v>1.69</v>
       </c>
       <c r="I38" s="7">
         <v>0.71</v>
       </c>
       <c r="J38" s="7">
-        <v>5078.1</v>
+        <v>5129.7</v>
       </c>
       <c r="K38" s="8">
         <v>0</v>
@@ -11672,28 +11675,28 @@
         <v>1483</v>
       </c>
       <c r="C39" s="8">
-        <v>8056514</v>
+        <v>7959841</v>
       </c>
       <c r="D39" s="8">
-        <v>1530738</v>
+        <v>1512370</v>
       </c>
       <c r="E39" s="8">
-        <v>6525776</v>
+        <v>6447471</v>
       </c>
       <c r="F39" s="7">
         <v>8.15</v>
       </c>
       <c r="G39" s="7">
-        <v>656.6</v>
+        <v>648.7</v>
       </c>
       <c r="H39" s="7">
-        <v>1.69</v>
+        <v>1.678</v>
       </c>
       <c r="I39" s="7">
         <v>0.71</v>
       </c>
       <c r="J39" s="7">
-        <v>4633.3</v>
+        <v>4577.7</v>
       </c>
       <c r="K39" s="8">
         <v>0</v>
@@ -11707,28 +11710,28 @@
         <v>1484</v>
       </c>
       <c r="C40" s="8">
-        <v>8812681</v>
+        <v>8870682</v>
       </c>
       <c r="D40" s="8">
-        <v>1674409</v>
+        <v>1685430</v>
       </c>
       <c r="E40" s="8">
-        <v>7138272</v>
+        <v>7185252</v>
       </c>
       <c r="F40" s="7">
         <v>8.15</v>
       </c>
       <c r="G40" s="7">
-        <v>718.2</v>
+        <v>723</v>
       </c>
       <c r="H40" s="7">
-        <v>1.678</v>
+        <v>1.68</v>
       </c>
       <c r="I40" s="7">
         <v>0.71</v>
       </c>
       <c r="J40" s="7">
-        <v>5068.2</v>
+        <v>5101.5</v>
       </c>
       <c r="K40" s="8">
         <v>0</v>
@@ -11742,28 +11745,28 @@
         <v>1485</v>
       </c>
       <c r="C41" s="8">
-        <v>8584531</v>
+        <v>8948827</v>
       </c>
       <c r="D41" s="8">
-        <v>1631061</v>
+        <v>1700277</v>
       </c>
       <c r="E41" s="8">
-        <v>6953470</v>
+        <v>7248550</v>
       </c>
       <c r="F41" s="7">
         <v>8.15</v>
       </c>
       <c r="G41" s="7">
-        <v>699.6</v>
+        <v>729.3</v>
       </c>
       <c r="H41" s="7">
-        <v>1.68</v>
+        <v>1.726</v>
       </c>
       <c r="I41" s="7">
         <v>0.71</v>
       </c>
       <c r="J41" s="7">
-        <v>4937</v>
+        <v>5146.5</v>
       </c>
       <c r="K41" s="8">
         <v>0</v>
@@ -11777,28 +11780,28 @@
         <v>1486</v>
       </c>
       <c r="C42" s="8">
-        <v>9247121</v>
+        <v>9285147</v>
       </c>
       <c r="D42" s="8">
-        <v>1756953</v>
+        <v>1764178</v>
       </c>
       <c r="E42" s="8">
-        <v>7490168</v>
+        <v>7520969</v>
       </c>
       <c r="F42" s="7">
         <v>8.15</v>
       </c>
       <c r="G42" s="7">
-        <v>753.6</v>
+        <v>756.7</v>
       </c>
       <c r="H42" s="7">
-        <v>1.726</v>
+        <v>1.724</v>
       </c>
       <c r="I42" s="7">
         <v>0.71</v>
       </c>
       <c r="J42" s="7">
-        <v>5318</v>
+        <v>5339.9</v>
       </c>
       <c r="K42" s="8">
         <v>0</v>
@@ -11812,28 +11815,28 @@
         <v>1487</v>
       </c>
       <c r="C43" s="8">
-        <v>8985626</v>
+        <v>8980606</v>
       </c>
       <c r="D43" s="8">
-        <v>1707269</v>
+        <v>1706315</v>
       </c>
       <c r="E43" s="8">
-        <v>7278357</v>
+        <v>7274291</v>
       </c>
       <c r="F43" s="7">
         <v>8.15</v>
       </c>
       <c r="G43" s="7">
-        <v>732.3</v>
+        <v>731.9</v>
       </c>
       <c r="H43" s="7">
-        <v>1.724</v>
+        <v>1.719</v>
       </c>
       <c r="I43" s="7">
         <v>0.71</v>
       </c>
       <c r="J43" s="7">
-        <v>5167.6</v>
+        <v>5164.7</v>
       </c>
       <c r="K43" s="8">
         <v>0</v>
@@ -11847,28 +11850,28 @@
         <v>1488</v>
       </c>
       <c r="C44" s="8">
-        <v>9279960</v>
+        <v>9173946</v>
       </c>
       <c r="D44" s="8">
-        <v>1763192</v>
+        <v>1743050</v>
       </c>
       <c r="E44" s="8">
-        <v>7516768</v>
+        <v>7430896</v>
       </c>
       <c r="F44" s="7">
         <v>8.15</v>
       </c>
       <c r="G44" s="7">
-        <v>756.3</v>
+        <v>747.7</v>
       </c>
       <c r="H44" s="7">
-        <v>1.719</v>
+        <v>1.669</v>
       </c>
       <c r="I44" s="7">
         <v>0.71</v>
       </c>
       <c r="J44" s="7">
-        <v>5336.9</v>
+        <v>5275.9</v>
       </c>
       <c r="K44" s="8">
         <v>0</v>
@@ -11882,28 +11885,28 @@
         <v>1489</v>
       </c>
       <c r="C45" s="8">
-        <v>9173946</v>
+        <v>9309261</v>
       </c>
       <c r="D45" s="8">
-        <v>1743050</v>
+        <v>1768760</v>
       </c>
       <c r="E45" s="8">
-        <v>7430896</v>
+        <v>7540501</v>
       </c>
       <c r="F45" s="7">
         <v>8.15</v>
       </c>
       <c r="G45" s="7">
-        <v>747.7</v>
+        <v>758.7</v>
       </c>
       <c r="H45" s="7">
-        <v>1.669</v>
+        <v>1.671</v>
       </c>
       <c r="I45" s="7">
         <v>0.71</v>
       </c>
       <c r="J45" s="7">
-        <v>5275.9</v>
+        <v>5353.8</v>
       </c>
       <c r="K45" s="8">
         <v>0</v>
@@ -11917,28 +11920,28 @@
         <v>1490</v>
       </c>
       <c r="C46" s="8">
-        <v>9008963</v>
+        <v>9155462</v>
       </c>
       <c r="D46" s="8">
-        <v>1711703</v>
+        <v>1739538</v>
       </c>
       <c r="E46" s="8">
-        <v>7297260</v>
+        <v>7415924</v>
       </c>
       <c r="F46" s="7">
         <v>8.15</v>
       </c>
       <c r="G46" s="7">
-        <v>734.2</v>
+        <v>746.2</v>
       </c>
       <c r="H46" s="7">
-        <v>1.671</v>
+        <v>1.68</v>
       </c>
       <c r="I46" s="7">
         <v>0.71</v>
       </c>
       <c r="J46" s="7">
-        <v>5181.1</v>
+        <v>5265.3</v>
       </c>
       <c r="K46" s="8">
         <v>0</v>
@@ -12027,16 +12030,16 @@
         <v>1482</v>
       </c>
       <c r="C2" s="8">
-        <v>8337502</v>
+        <v>8849728</v>
       </c>
       <c r="D2" s="7">
-        <v>1.762</v>
+        <v>1.828</v>
       </c>
       <c r="E2" s="8">
-        <v>1500750</v>
+        <v>1592951</v>
       </c>
       <c r="F2" s="8">
-        <v>6836752</v>
+        <v>7256777</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>1503</v>
@@ -12048,7 +12051,7 @@
         <v>62</v>
       </c>
       <c r="J2" s="7">
-        <v>212.9</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12059,16 +12062,16 @@
         <v>1483</v>
       </c>
       <c r="C3" s="8">
-        <v>7993303</v>
+        <v>8105665</v>
       </c>
       <c r="D3" s="7">
-        <v>1.828</v>
+        <v>1.839</v>
       </c>
       <c r="E3" s="8">
-        <v>1438794</v>
+        <v>1459019</v>
       </c>
       <c r="F3" s="8">
-        <v>6554509</v>
+        <v>6646646</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>1503</v>
@@ -12080,7 +12083,7 @@
         <v>62</v>
       </c>
       <c r="J3" s="7">
-        <v>226</v>
+        <v>229.2</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12091,16 +12094,16 @@
         <v>1484</v>
       </c>
       <c r="C4" s="8">
-        <v>8974129</v>
+        <v>8568952</v>
       </c>
       <c r="D4" s="7">
-        <v>1.839</v>
+        <v>1.773</v>
       </c>
       <c r="E4" s="8">
-        <v>1615343</v>
+        <v>1542411</v>
       </c>
       <c r="F4" s="8">
-        <v>7358786</v>
+        <v>7026541</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>1503</v>
@@ -12112,7 +12115,7 @@
         <v>62</v>
       </c>
       <c r="J4" s="7">
-        <v>229.2</v>
+        <v>218.8</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12123,16 +12126,16 @@
         <v>1485</v>
       </c>
       <c r="C5" s="8">
-        <v>8292534</v>
+        <v>8435022</v>
       </c>
       <c r="D5" s="7">
-        <v>1.773</v>
+        <v>1.796</v>
       </c>
       <c r="E5" s="8">
-        <v>1492656</v>
+        <v>1518304</v>
       </c>
       <c r="F5" s="8">
-        <v>6799878</v>
+        <v>6916718</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>1503</v>
@@ -12144,7 +12147,7 @@
         <v>62</v>
       </c>
       <c r="J5" s="7">
-        <v>243.8</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12155,16 +12158,16 @@
         <v>1486</v>
       </c>
       <c r="C6" s="8">
-        <v>8716189</v>
+        <v>9026349</v>
       </c>
       <c r="D6" s="7">
-        <v>1.796</v>
+        <v>1.841</v>
       </c>
       <c r="E6" s="8">
-        <v>1568914</v>
+        <v>1624743</v>
       </c>
       <c r="F6" s="8">
-        <v>7147275</v>
+        <v>7401606</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>1503</v>
@@ -12176,7 +12179,7 @@
         <v>62</v>
       </c>
       <c r="J6" s="7">
-        <v>251.9</v>
+        <v>260.8</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12187,16 +12190,16 @@
         <v>1487</v>
       </c>
       <c r="C7" s="8">
-        <v>8735177</v>
+        <v>8787919</v>
       </c>
       <c r="D7" s="7">
-        <v>1.841</v>
+        <v>1.839</v>
       </c>
       <c r="E7" s="8">
-        <v>1572332</v>
+        <v>1581826</v>
       </c>
       <c r="F7" s="8">
-        <v>7162845</v>
+        <v>7206093</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>1503</v>
@@ -12208,7 +12211,7 @@
         <v>62</v>
       </c>
       <c r="J7" s="7">
-        <v>250.7</v>
+        <v>252.2</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12219,16 +12222,16 @@
         <v>1488</v>
       </c>
       <c r="C8" s="8">
-        <v>9080850</v>
+        <v>9387774</v>
       </c>
       <c r="D8" s="7">
-        <v>1.839</v>
+        <v>1.876</v>
       </c>
       <c r="E8" s="8">
-        <v>1634553</v>
+        <v>1689799</v>
       </c>
       <c r="F8" s="8">
-        <v>7446297</v>
+        <v>7697975</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>1503</v>
@@ -12240,7 +12243,7 @@
         <v>62</v>
       </c>
       <c r="J8" s="7">
-        <v>240</v>
+        <v>248.2</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12251,16 +12254,16 @@
         <v>1489</v>
       </c>
       <c r="C9" s="8">
-        <v>9387774</v>
+        <v>9323969</v>
       </c>
       <c r="D9" s="7">
-        <v>1.876</v>
+        <v>1.816</v>
       </c>
       <c r="E9" s="8">
-        <v>1689799</v>
+        <v>1678314</v>
       </c>
       <c r="F9" s="8">
-        <v>7697975</v>
+        <v>7645655</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>1503</v>
@@ -12272,7 +12275,7 @@
         <v>62</v>
       </c>
       <c r="J9" s="7">
-        <v>246.1</v>
+        <v>244.4</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12283,16 +12286,16 @@
         <v>1490</v>
       </c>
       <c r="C10" s="8">
-        <v>9023196</v>
+        <v>9379458</v>
       </c>
       <c r="D10" s="7">
-        <v>1.816</v>
+        <v>1.865</v>
       </c>
       <c r="E10" s="8">
-        <v>1624175</v>
+        <v>1688302</v>
       </c>
       <c r="F10" s="8">
-        <v>7399021</v>
+        <v>7691156</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>1503</v>
@@ -12304,7 +12307,7 @@
         <v>62</v>
       </c>
       <c r="J10" s="7">
-        <v>248.6</v>
+        <v>258.4</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12315,16 +12318,16 @@
         <v>1482</v>
       </c>
       <c r="C11" s="8">
-        <v>7141311</v>
+        <v>7421269</v>
       </c>
       <c r="D11" s="7">
-        <v>2.088</v>
+        <v>2.116</v>
       </c>
       <c r="E11" s="8">
-        <v>856957</v>
+        <v>890552</v>
       </c>
       <c r="F11" s="8">
-        <v>6284354</v>
+        <v>6530717</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>1503</v>
@@ -12336,7 +12339,7 @@
         <v>62</v>
       </c>
       <c r="J11" s="7">
-        <v>182.4</v>
+        <v>189.5</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12347,16 +12350,16 @@
         <v>1483</v>
       </c>
       <c r="C12" s="8">
-        <v>6703082</v>
+        <v>6725057</v>
       </c>
       <c r="D12" s="7">
-        <v>2.116</v>
+        <v>2.091</v>
       </c>
       <c r="E12" s="8">
-        <v>804370</v>
+        <v>807007</v>
       </c>
       <c r="F12" s="8">
-        <v>5898712</v>
+        <v>5918050</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>1503</v>
@@ -12368,7 +12371,7 @@
         <v>62</v>
       </c>
       <c r="J12" s="7">
-        <v>189.5</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12379,16 +12382,16 @@
         <v>1484</v>
       </c>
       <c r="C13" s="8">
-        <v>7445599</v>
+        <v>7420556</v>
       </c>
       <c r="D13" s="7">
-        <v>2.091</v>
+        <v>2.074</v>
       </c>
       <c r="E13" s="8">
-        <v>893472</v>
+        <v>890467</v>
       </c>
       <c r="F13" s="8">
-        <v>6552127</v>
+        <v>6530089</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>1503</v>
@@ -12400,7 +12403,7 @@
         <v>62</v>
       </c>
       <c r="J13" s="7">
-        <v>190.1</v>
+        <v>189.5</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12411,16 +12414,16 @@
         <v>1485</v>
       </c>
       <c r="C14" s="8">
-        <v>7181184</v>
+        <v>7342891</v>
       </c>
       <c r="D14" s="7">
-        <v>2.074</v>
+        <v>2.095</v>
       </c>
       <c r="E14" s="8">
-        <v>861742</v>
+        <v>881147</v>
       </c>
       <c r="F14" s="8">
-        <v>6319442</v>
+        <v>6461744</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>1503</v>
@@ -12432,7 +12435,7 @@
         <v>62</v>
       </c>
       <c r="J14" s="7">
-        <v>211.1</v>
+        <v>215.9</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12443,16 +12446,16 @@
         <v>1486</v>
       </c>
       <c r="C15" s="8">
-        <v>7587654</v>
+        <v>7639658</v>
       </c>
       <c r="D15" s="7">
-        <v>2.095</v>
+        <v>2.122</v>
       </c>
       <c r="E15" s="8">
-        <v>910519</v>
+        <v>916759</v>
       </c>
       <c r="F15" s="8">
-        <v>6677135</v>
+        <v>6722899</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>1503</v>
@@ -12464,7 +12467,7 @@
         <v>62</v>
       </c>
       <c r="J15" s="7">
-        <v>219.3</v>
+        <v>220.8</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12475,16 +12478,16 @@
         <v>1487</v>
       </c>
       <c r="C16" s="8">
-        <v>7393218</v>
+        <v>7429439</v>
       </c>
       <c r="D16" s="7">
-        <v>2.122</v>
+        <v>2.085</v>
       </c>
       <c r="E16" s="8">
-        <v>887186</v>
+        <v>891533</v>
       </c>
       <c r="F16" s="8">
-        <v>6506032</v>
+        <v>6537906</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>1503</v>
@@ -12496,7 +12499,7 @@
         <v>62</v>
       </c>
       <c r="J16" s="7">
-        <v>212.2</v>
+        <v>213.3</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12507,16 +12510,16 @@
         <v>1488</v>
       </c>
       <c r="C17" s="8">
-        <v>7677087</v>
+        <v>7848084</v>
       </c>
       <c r="D17" s="7">
-        <v>2.085</v>
+        <v>2.125</v>
       </c>
       <c r="E17" s="8">
-        <v>921251</v>
+        <v>941771</v>
       </c>
       <c r="F17" s="8">
-        <v>6755836</v>
+        <v>6906313</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>1503</v>
@@ -12528,7 +12531,7 @@
         <v>62</v>
       </c>
       <c r="J17" s="7">
-        <v>202.9</v>
+        <v>207.5</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12539,16 +12542,16 @@
         <v>1489</v>
       </c>
       <c r="C18" s="8">
-        <v>7848084</v>
+        <v>7875918</v>
       </c>
       <c r="D18" s="7">
-        <v>2.125</v>
+        <v>2.121</v>
       </c>
       <c r="E18" s="8">
-        <v>941770</v>
+        <v>945110</v>
       </c>
       <c r="F18" s="8">
-        <v>6906314</v>
+        <v>6930808</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>1503</v>
@@ -12560,7 +12563,7 @@
         <v>62</v>
       </c>
       <c r="J18" s="7">
-        <v>205.7</v>
+        <v>206.4</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12571,16 +12574,16 @@
         <v>1490</v>
       </c>
       <c r="C19" s="8">
-        <v>7621856</v>
+        <v>7587855</v>
       </c>
       <c r="D19" s="7">
-        <v>2.121</v>
+        <v>2.096</v>
       </c>
       <c r="E19" s="8">
-        <v>914623</v>
+        <v>910543</v>
       </c>
       <c r="F19" s="8">
-        <v>6707233</v>
+        <v>6677312</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>1503</v>
@@ -12592,7 +12595,7 @@
         <v>62</v>
       </c>
       <c r="J19" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12603,16 +12606,16 @@
         <v>1482</v>
       </c>
       <c r="C20" s="8">
-        <v>9311328</v>
+        <v>9543092</v>
       </c>
       <c r="D20" s="7">
-        <v>2.417</v>
+        <v>2.453</v>
       </c>
       <c r="E20" s="8">
-        <v>838019</v>
+        <v>858878</v>
       </c>
       <c r="F20" s="8">
-        <v>8473309</v>
+        <v>8684214</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>1503</v>
@@ -12624,7 +12627,7 @@
         <v>84</v>
       </c>
       <c r="J20" s="7">
-        <v>237.8</v>
+        <v>243.7</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12635,16 +12638,16 @@
         <v>1483</v>
       </c>
       <c r="C21" s="8">
-        <v>8619567</v>
+        <v>8610699</v>
       </c>
       <c r="D21" s="7">
-        <v>2.453</v>
+        <v>2.49</v>
       </c>
       <c r="E21" s="8">
-        <v>775761</v>
+        <v>774963</v>
       </c>
       <c r="F21" s="8">
-        <v>7843806</v>
+        <v>7835736</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>1503</v>
@@ -12656,7 +12659,7 @@
         <v>84</v>
       </c>
       <c r="J21" s="7">
-        <v>243.7</v>
+        <v>243.5</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12667,16 +12670,16 @@
         <v>1484</v>
       </c>
       <c r="C22" s="8">
-        <v>9533274</v>
+        <v>9821291</v>
       </c>
       <c r="D22" s="7">
-        <v>2.49</v>
+        <v>2.486</v>
       </c>
       <c r="E22" s="8">
-        <v>857995</v>
+        <v>883917</v>
       </c>
       <c r="F22" s="8">
-        <v>8675279</v>
+        <v>8937374</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>1503</v>
@@ -12688,7 +12691,7 @@
         <v>84</v>
       </c>
       <c r="J22" s="7">
-        <v>243.5</v>
+        <v>250.8</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12699,16 +12702,16 @@
         <v>1485</v>
       </c>
       <c r="C23" s="8">
-        <v>9504475</v>
+        <v>9552539</v>
       </c>
       <c r="D23" s="7">
-        <v>2.486</v>
+        <v>2.485</v>
       </c>
       <c r="E23" s="8">
-        <v>855403</v>
+        <v>859729</v>
       </c>
       <c r="F23" s="8">
-        <v>8649072</v>
+        <v>8692810</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>1503</v>
@@ -12720,7 +12723,7 @@
         <v>84</v>
       </c>
       <c r="J23" s="7">
-        <v>279.4</v>
+        <v>280.8</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12731,16 +12734,16 @@
         <v>1486</v>
       </c>
       <c r="C24" s="8">
-        <v>9870957</v>
+        <v>9569700</v>
       </c>
       <c r="D24" s="7">
-        <v>2.485</v>
+        <v>2.45</v>
       </c>
       <c r="E24" s="8">
-        <v>888386</v>
+        <v>861273</v>
       </c>
       <c r="F24" s="8">
-        <v>8982571</v>
+        <v>8708427</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>1503</v>
@@ -12752,7 +12755,7 @@
         <v>84</v>
       </c>
       <c r="J24" s="7">
-        <v>285.2</v>
+        <v>276.5</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12763,16 +12766,16 @@
         <v>1487</v>
       </c>
       <c r="C25" s="8">
-        <v>9261000</v>
+        <v>9547949</v>
       </c>
       <c r="D25" s="7">
-        <v>2.45</v>
+        <v>2.488</v>
       </c>
       <c r="E25" s="8">
-        <v>833490</v>
+        <v>859315</v>
       </c>
       <c r="F25" s="8">
-        <v>8427510</v>
+        <v>8688634</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>1503</v>
@@ -12784,7 +12787,7 @@
         <v>84</v>
       </c>
       <c r="J25" s="7">
-        <v>265.8</v>
+        <v>274.1</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12795,16 +12798,16 @@
         <v>1488</v>
       </c>
       <c r="C26" s="8">
-        <v>9866214</v>
+        <v>10100568</v>
       </c>
       <c r="D26" s="7">
-        <v>2.488</v>
+        <v>2.481</v>
       </c>
       <c r="E26" s="8">
-        <v>887959</v>
+        <v>909051</v>
       </c>
       <c r="F26" s="8">
-        <v>8978255</v>
+        <v>9191517</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>1503</v>
@@ -12816,7 +12819,7 @@
         <v>84</v>
       </c>
       <c r="J26" s="7">
-        <v>260.8</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12827,16 +12830,16 @@
         <v>1489</v>
       </c>
       <c r="C27" s="8">
-        <v>10100568</v>
+        <v>9827477</v>
       </c>
       <c r="D27" s="7">
-        <v>2.481</v>
+        <v>2.425</v>
       </c>
       <c r="E27" s="8">
-        <v>909051</v>
+        <v>884473</v>
       </c>
       <c r="F27" s="8">
-        <v>9191517</v>
+        <v>8943004</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>1503</v>
@@ -12848,7 +12851,7 @@
         <v>84</v>
       </c>
       <c r="J27" s="7">
-        <v>264.7</v>
+        <v>257.6</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12859,16 +12862,16 @@
         <v>1490</v>
       </c>
       <c r="C28" s="8">
-        <v>9510462</v>
+        <v>9898362</v>
       </c>
       <c r="D28" s="7">
-        <v>2.425</v>
+        <v>2.511</v>
       </c>
       <c r="E28" s="8">
-        <v>855941</v>
+        <v>890852</v>
       </c>
       <c r="F28" s="8">
-        <v>8654521</v>
+        <v>9007510</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>1503</v>
@@ -12880,7 +12883,7 @@
         <v>84</v>
       </c>
       <c r="J28" s="7">
-        <v>262</v>
+        <v>272.7</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12891,16 +12894,16 @@
         <v>1482</v>
       </c>
       <c r="C29" s="8">
-        <v>4897615</v>
+        <v>5151094</v>
       </c>
       <c r="D29" s="7">
-        <v>0.912</v>
+        <v>0.962</v>
       </c>
       <c r="E29" s="8">
-        <v>2252903</v>
+        <v>2369503</v>
       </c>
       <c r="F29" s="8">
-        <v>2644712</v>
+        <v>2781591</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>1503</v>
@@ -12912,7 +12915,7 @@
         <v>68</v>
       </c>
       <c r="J29" s="7">
-        <v>125.1</v>
+        <v>131.5</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12923,16 +12926,16 @@
         <v>1483</v>
       </c>
       <c r="C30" s="8">
-        <v>4652601</v>
+        <v>4571582</v>
       </c>
       <c r="D30" s="7">
-        <v>0.962</v>
+        <v>0.93</v>
       </c>
       <c r="E30" s="8">
-        <v>2140196</v>
+        <v>2102927</v>
       </c>
       <c r="F30" s="8">
-        <v>2512405</v>
+        <v>2468655</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>1503</v>
@@ -12944,7 +12947,7 @@
         <v>68</v>
       </c>
       <c r="J30" s="7">
-        <v>131.5</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12955,16 +12958,16 @@
         <v>1484</v>
       </c>
       <c r="C31" s="8">
-        <v>5061395</v>
+        <v>5298735</v>
       </c>
       <c r="D31" s="7">
-        <v>0.93</v>
+        <v>0.967</v>
       </c>
       <c r="E31" s="8">
-        <v>2328242</v>
+        <v>2437418</v>
       </c>
       <c r="F31" s="8">
-        <v>2733153</v>
+        <v>2861317</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>1503</v>
@@ -12976,7 +12979,7 @@
         <v>68</v>
       </c>
       <c r="J31" s="7">
-        <v>129.3</v>
+        <v>135.3</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12987,16 +12990,16 @@
         <v>1485</v>
       </c>
       <c r="C32" s="8">
-        <v>5127808</v>
+        <v>4913758</v>
       </c>
       <c r="D32" s="7">
-        <v>0.967</v>
+        <v>0.924</v>
       </c>
       <c r="E32" s="8">
-        <v>2358792</v>
+        <v>2260329</v>
       </c>
       <c r="F32" s="8">
-        <v>2769016</v>
+        <v>2653429</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>1503</v>
@@ -13008,7 +13011,7 @@
         <v>68</v>
       </c>
       <c r="J32" s="7">
-        <v>150.7</v>
+        <v>144.5</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -13019,16 +13022,16 @@
         <v>1486</v>
       </c>
       <c r="C33" s="8">
-        <v>5077550</v>
+        <v>5286074</v>
       </c>
       <c r="D33" s="7">
-        <v>0.924</v>
+        <v>0.934</v>
       </c>
       <c r="E33" s="8">
-        <v>2335673</v>
+        <v>2431594</v>
       </c>
       <c r="F33" s="8">
-        <v>2741877</v>
+        <v>2854480</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>1503</v>
@@ -13040,7 +13043,7 @@
         <v>68</v>
       </c>
       <c r="J33" s="7">
-        <v>146.7</v>
+        <v>152.8</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -13051,16 +13054,16 @@
         <v>1487</v>
       </c>
       <c r="C34" s="8">
-        <v>5115555</v>
+        <v>5007537</v>
       </c>
       <c r="D34" s="7">
-        <v>0.934</v>
+        <v>0.912</v>
       </c>
       <c r="E34" s="8">
-        <v>2353155</v>
+        <v>2303467</v>
       </c>
       <c r="F34" s="8">
-        <v>2762400</v>
+        <v>2704070</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>1503</v>
@@ -13072,7 +13075,7 @@
         <v>68</v>
       </c>
       <c r="J34" s="7">
-        <v>146.8</v>
+        <v>143.7</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -13083,16 +13086,16 @@
         <v>1488</v>
       </c>
       <c r="C35" s="8">
-        <v>5174455</v>
+        <v>5170136</v>
       </c>
       <c r="D35" s="7">
-        <v>0.912</v>
+        <v>0.911</v>
       </c>
       <c r="E35" s="8">
-        <v>2380250</v>
+        <v>2378263</v>
       </c>
       <c r="F35" s="8">
-        <v>2794205</v>
+        <v>2791873</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>1503</v>
@@ -13104,7 +13107,7 @@
         <v>68</v>
       </c>
       <c r="J35" s="7">
-        <v>136.8</v>
+        <v>136.7</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -13115,16 +13118,16 @@
         <v>1489</v>
       </c>
       <c r="C36" s="8">
-        <v>5170136</v>
+        <v>5568694</v>
       </c>
       <c r="D36" s="7">
-        <v>0.911</v>
+        <v>0.982</v>
       </c>
       <c r="E36" s="8">
-        <v>2378263</v>
+        <v>2561600</v>
       </c>
       <c r="F36" s="8">
-        <v>2791873</v>
+        <v>3007094</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>1503</v>
@@ -13136,7 +13139,7 @@
         <v>68</v>
       </c>
       <c r="J36" s="7">
-        <v>135.5</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -13147,16 +13150,16 @@
         <v>1490</v>
       </c>
       <c r="C37" s="8">
-        <v>5389059</v>
+        <v>5121935</v>
       </c>
       <c r="D37" s="7">
-        <v>0.982</v>
+        <v>0.927</v>
       </c>
       <c r="E37" s="8">
-        <v>2478967</v>
+        <v>2356090</v>
       </c>
       <c r="F37" s="8">
-        <v>2910092</v>
+        <v>2765845</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>1503</v>
@@ -13168,7 +13171,7 @@
         <v>68</v>
       </c>
       <c r="J37" s="7">
-        <v>148.4</v>
+        <v>141.1</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -13179,16 +13182,16 @@
         <v>1482</v>
       </c>
       <c r="C38" s="8">
-        <v>10189665</v>
+        <v>10360588</v>
       </c>
       <c r="D38" s="7">
-        <v>1.926</v>
+        <v>1.963</v>
       </c>
       <c r="E38" s="8">
-        <v>2139830</v>
+        <v>2175724</v>
       </c>
       <c r="F38" s="8">
-        <v>8049835</v>
+        <v>8184864</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>1503</v>
@@ -13200,7 +13203,7 @@
         <v>81</v>
       </c>
       <c r="J38" s="7">
-        <v>260.2</v>
+        <v>264.6</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -13211,16 +13214,16 @@
         <v>1483</v>
       </c>
       <c r="C39" s="8">
-        <v>9357951</v>
+        <v>9425629</v>
       </c>
       <c r="D39" s="7">
-        <v>1.963</v>
+        <v>1.987</v>
       </c>
       <c r="E39" s="8">
-        <v>1965170</v>
+        <v>1979382</v>
       </c>
       <c r="F39" s="8">
-        <v>7392781</v>
+        <v>7446247</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>1503</v>
@@ -13232,7 +13235,7 @@
         <v>81</v>
       </c>
       <c r="J39" s="7">
-        <v>264.6</v>
+        <v>266.5</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -13243,16 +13246,16 @@
         <v>1484</v>
       </c>
       <c r="C40" s="8">
-        <v>10435517</v>
+        <v>10211845</v>
       </c>
       <c r="D40" s="7">
-        <v>1.987</v>
+        <v>1.934</v>
       </c>
       <c r="E40" s="8">
-        <v>2191459</v>
+        <v>2144488</v>
       </c>
       <c r="F40" s="8">
-        <v>8244058</v>
+        <v>8067357</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>1503</v>
@@ -13264,7 +13267,7 @@
         <v>81</v>
       </c>
       <c r="J40" s="7">
-        <v>266.5</v>
+        <v>260.8</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -13275,16 +13278,16 @@
         <v>1485</v>
       </c>
       <c r="C41" s="8">
-        <v>9882431</v>
+        <v>10255376</v>
       </c>
       <c r="D41" s="7">
-        <v>1.934</v>
+        <v>1.978</v>
       </c>
       <c r="E41" s="8">
-        <v>2075311</v>
+        <v>2153629</v>
       </c>
       <c r="F41" s="8">
-        <v>7807120</v>
+        <v>8101747</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>1503</v>
@@ -13296,7 +13299,7 @@
         <v>81</v>
       </c>
       <c r="J41" s="7">
-        <v>290.5</v>
+        <v>301.5</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -13307,16 +13310,16 @@
         <v>1486</v>
       </c>
       <c r="C42" s="8">
-        <v>10597222</v>
+        <v>10426940</v>
       </c>
       <c r="D42" s="7">
-        <v>1.978</v>
+        <v>1.936</v>
       </c>
       <c r="E42" s="8">
-        <v>2225417</v>
+        <v>2189658</v>
       </c>
       <c r="F42" s="8">
-        <v>8371805</v>
+        <v>8237282</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>1503</v>
@@ -13328,7 +13331,7 @@
         <v>81</v>
       </c>
       <c r="J42" s="7">
-        <v>306.2</v>
+        <v>301.3</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -13339,16 +13342,16 @@
         <v>1487</v>
       </c>
       <c r="C43" s="8">
-        <v>10090587</v>
+        <v>10145629</v>
       </c>
       <c r="D43" s="7">
-        <v>1.936</v>
+        <v>1.942</v>
       </c>
       <c r="E43" s="8">
-        <v>2119023</v>
+        <v>2130582</v>
       </c>
       <c r="F43" s="8">
-        <v>7971564</v>
+        <v>8015047</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>1503</v>
@@ -13360,7 +13363,7 @@
         <v>81</v>
       </c>
       <c r="J43" s="7">
-        <v>289.6</v>
+        <v>291.2</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -13371,16 +13374,16 @@
         <v>1488</v>
       </c>
       <c r="C44" s="8">
-        <v>10483817</v>
+        <v>10773477</v>
       </c>
       <c r="D44" s="7">
-        <v>1.942</v>
+        <v>1.96</v>
       </c>
       <c r="E44" s="8">
-        <v>2201602</v>
+        <v>2262431</v>
       </c>
       <c r="F44" s="8">
-        <v>8282215</v>
+        <v>8511046</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>1503</v>
@@ -13392,7 +13395,7 @@
         <v>81</v>
       </c>
       <c r="J44" s="7">
-        <v>277.1</v>
+        <v>284.8</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -13403,16 +13406,16 @@
         <v>1489</v>
       </c>
       <c r="C45" s="8">
-        <v>10773477</v>
+        <v>10902588</v>
       </c>
       <c r="D45" s="7">
-        <v>1.96</v>
+        <v>1.957</v>
       </c>
       <c r="E45" s="8">
-        <v>2262430</v>
+        <v>2289543</v>
       </c>
       <c r="F45" s="8">
-        <v>8511047</v>
+        <v>8613045</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>1503</v>
@@ -13424,7 +13427,7 @@
         <v>81</v>
       </c>
       <c r="J45" s="7">
-        <v>282.4</v>
+        <v>285.8</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -13435,16 +13438,16 @@
         <v>1490</v>
       </c>
       <c r="C46" s="8">
-        <v>10550892</v>
+        <v>10648675</v>
       </c>
       <c r="D46" s="7">
-        <v>1.957</v>
+        <v>1.954</v>
       </c>
       <c r="E46" s="8">
-        <v>2215687</v>
+        <v>2236221</v>
       </c>
       <c r="F46" s="8">
-        <v>8335205</v>
+        <v>8412454</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>1503</v>
@@ -13456,7 +13459,7 @@
         <v>81</v>
       </c>
       <c r="J46" s="7">
-        <v>290.6</v>
+        <v>293.3</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -17795,7 +17798,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I125"/>
+  <dimension ref="A1:I130"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.6796875"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -18246,7 +18249,7 @@
         <v>61</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>1482</v>
+        <v>1930</v>
       </c>
       <c r="C17" s="8">
         <v>6360</v>
@@ -18273,7 +18276,7 @@
         <v>61</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="C18" s="8">
         <v>6507</v>
@@ -18300,7 +18303,7 @@
         <v>61</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="C19" s="8">
         <v>6559</v>
@@ -18327,7 +18330,7 @@
         <v>61</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="C20" s="8">
         <v>6496</v>
@@ -18354,7 +18357,7 @@
         <v>61</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="C21" s="8">
         <v>6523</v>
@@ -18381,7 +18384,7 @@
         <v>61</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="C22" s="8">
         <v>6590</v>
@@ -18402,7 +18405,7 @@
         <v>99.9969</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -18410,7 +18413,7 @@
         <v>61</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="C23" s="8">
         <v>6637</v>
@@ -18431,7 +18434,7 @@
         <v>99.9724</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -18439,7 +18442,7 @@
         <v>61</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="C24" s="8">
         <v>6726</v>
@@ -18460,7 +18463,7 @@
         <v>99.9886</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -18468,7 +18471,7 @@
         <v>61</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="C25" s="8">
         <v>6901</v>
@@ -18489,7 +18492,7 @@
         <v>99.9809</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -18902,7 +18905,7 @@
         <v>69</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>1482</v>
+        <v>1930</v>
       </c>
       <c r="C41" s="8">
         <v>4597</v>
@@ -18929,7 +18932,7 @@
         <v>69</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="C42" s="8">
         <v>4714</v>
@@ -18956,7 +18959,7 @@
         <v>69</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="C43" s="8">
         <v>4786</v>
@@ -18983,7 +18986,7 @@
         <v>69</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="C44" s="8">
         <v>4809</v>
@@ -19010,7 +19013,7 @@
         <v>69</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="C45" s="8">
         <v>4868</v>
@@ -19037,7 +19040,7 @@
         <v>69</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="C46" s="8">
         <v>4839</v>
@@ -19064,7 +19067,7 @@
         <v>69</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="C47" s="8">
         <v>4949</v>
@@ -19091,7 +19094,7 @@
         <v>69</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="C48" s="8">
         <v>4964</v>
@@ -19118,7 +19121,7 @@
         <v>69</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="C49" s="8">
         <v>4991</v>
@@ -19550,7 +19553,7 @@
         <v>73</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>1482</v>
+        <v>1930</v>
       </c>
       <c r="C65" s="8">
         <v>5178</v>
@@ -19577,7 +19580,7 @@
         <v>73</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="C66" s="8">
         <v>5229</v>
@@ -19604,7 +19607,7 @@
         <v>73</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="C67" s="8">
         <v>5146</v>
@@ -19631,7 +19634,7 @@
         <v>73</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="C68" s="8">
         <v>5310</v>
@@ -19658,7 +19661,7 @@
         <v>73</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="C69" s="8">
         <v>5339</v>
@@ -19685,7 +19688,7 @@
         <v>73</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="C70" s="8">
         <v>5250</v>
@@ -19712,7 +19715,7 @@
         <v>73</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="C71" s="8">
         <v>5330</v>
@@ -19739,7 +19742,7 @@
         <v>73</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="C72" s="8">
         <v>5472</v>
@@ -19766,7 +19769,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="C73" s="8">
         <v>5447</v>
@@ -20198,7 +20201,7 @@
         <v>79</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>1482</v>
+        <v>1930</v>
       </c>
       <c r="C89" s="8">
         <v>7218</v>
@@ -20225,7 +20228,7 @@
         <v>79</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="C90" s="8">
         <v>7197</v>
@@ -20252,7 +20255,7 @@
         <v>79</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="C91" s="8">
         <v>7315</v>
@@ -20279,7 +20282,7 @@
         <v>79</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="C92" s="8">
         <v>7365</v>
@@ -20306,7 +20309,7 @@
         <v>79</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="C93" s="8">
         <v>7386</v>
@@ -20333,7 +20336,7 @@
         <v>79</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="C94" s="8">
         <v>7607</v>
@@ -20360,7 +20363,7 @@
         <v>79</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="C95" s="8">
         <v>7626</v>
@@ -20387,7 +20390,7 @@
         <v>79</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="C96" s="8">
         <v>7628</v>
@@ -20414,7 +20417,7 @@
         <v>79</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="C97" s="8">
         <v>7622</v>
@@ -20846,7 +20849,7 @@
         <v>85</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>1482</v>
+        <v>1930</v>
       </c>
       <c r="C113" s="8">
         <v>7111</v>
@@ -20873,7 +20876,7 @@
         <v>85</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="C114" s="8">
         <v>7094</v>
@@ -20900,7 +20903,7 @@
         <v>85</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="C115" s="8">
         <v>7059</v>
@@ -20927,7 +20930,7 @@
         <v>85</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="C116" s="8">
         <v>7097</v>
@@ -20954,7 +20957,7 @@
         <v>85</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="C117" s="8">
         <v>7201</v>
@@ -20981,7 +20984,7 @@
         <v>85</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="C118" s="8">
         <v>7239</v>
@@ -21008,7 +21011,7 @@
         <v>85</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="C119" s="8">
         <v>7256</v>
@@ -21035,7 +21038,7 @@
         <v>85</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="C120" s="8">
         <v>7388</v>
@@ -21062,7 +21065,7 @@
         <v>85</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="C121" s="8">
         <v>7488</v>
@@ -21084,19 +21087,152 @@
       </c>
       <c r="I121" s="6"/>
     </row>
-    <row r="123" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A123" s="9" t="s">
+    <row r="122" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C122" s="8">
+        <v>6985</v>
+      </c>
+      <c r="D122" s="8">
+        <v>11483</v>
+      </c>
+      <c r="E122" s="7">
+        <v>1.644</v>
+      </c>
+      <c r="F122" s="7">
+        <v>1.865</v>
+      </c>
+      <c r="G122" s="7">
+        <v>69.9</v>
+      </c>
+      <c r="H122" s="7">
+        <v>99.9802</v>
+      </c>
+      <c r="I122" t="s">
         <v>1931</v>
       </c>
     </row>
-    <row r="124" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A124" s="9" t="s">
+    <row r="123" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C123" s="8">
+        <v>5028</v>
+      </c>
+      <c r="D123" s="8">
+        <v>8724</v>
+      </c>
+      <c r="E123" s="7">
+        <v>1.735</v>
+      </c>
+      <c r="F123" s="7">
+        <v>2.096</v>
+      </c>
+      <c r="G123" s="7">
+        <v>83.8</v>
+      </c>
+      <c r="H123" s="7">
+        <v>99.9818</v>
+      </c>
+    </row>
+    <row r="124" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C124" s="8">
+        <v>5475</v>
+      </c>
+      <c r="D124" s="8">
+        <v>8864</v>
+      </c>
+      <c r="E124" s="7">
+        <v>1.619</v>
+      </c>
+      <c r="F124" s="7">
+        <v>2.511</v>
+      </c>
+      <c r="G124" s="7">
+        <v>68.4</v>
+      </c>
+      <c r="H124" s="7">
+        <v>99.9851</v>
+      </c>
+    </row>
+    <row r="125" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C125" s="8">
+        <v>7674</v>
+      </c>
+      <c r="D125" s="8">
+        <v>10214</v>
+      </c>
+      <c r="E125" s="7">
+        <v>1.331</v>
+      </c>
+      <c r="F125" s="7">
+        <v>0.927</v>
+      </c>
+      <c r="G125" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="H125" s="7">
+        <v>99.9851</v>
+      </c>
+    </row>
+    <row r="126" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C126" s="8">
+        <v>7569</v>
+      </c>
+      <c r="D126" s="8">
+        <v>12716</v>
+      </c>
+      <c r="E126" s="7">
+        <v>1.68</v>
+      </c>
+      <c r="F126" s="7">
+        <v>1.954</v>
+      </c>
+      <c r="G126" s="7">
+        <v>84.1</v>
+      </c>
+      <c r="H126" s="7">
+        <v>99.985</v>
+      </c>
+    </row>
+    <row r="128" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" s="9" t="s">
         <v>1932</v>
       </c>
     </row>
-    <row r="125" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A125" s="9" t="s">
+    <row r="129" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" s="9" t="s">
         <v>1933</v>
+      </c>
+    </row>
+    <row r="130" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" s="9" t="s">
+        <v>1934</v>
       </c>
     </row>
   </sheetData>
@@ -21117,18 +21253,18 @@
   <sheetData>
     <row r="1" ht="17.35" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>50</v>
@@ -21136,7 +21272,7 @@
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="B4" s="6">
         <f>SUMIFS(03_rows!O2:O25,03_rows!Q2:Q25,"structural")</f>
@@ -21152,7 +21288,7 @@
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="B5" s="6">
         <f>SUMIFS(03_rows!O2:O25,03_rows!Q2:Q25,"planned headroom")</f>
@@ -21168,7 +21304,7 @@
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="B6" s="6">
         <f>SUM(03_rows!H2:H25)</f>
@@ -21184,7 +21320,7 @@
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="B7" s="6">
         <f>SUMIFS(03_rows!G2:G25,03_rows!B2:B25,"MUM-1-H4")</f>
@@ -21200,7 +21336,7 @@
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="B8" s="6">
         <f>SUMIFS(03_rows!I2:I25,03_rows!B2:B25,"MUM-1-H4")-SUMIFS(03_rows!H2:H25,03_rows!B2:B25,"MUM-1-H4")</f>
@@ -21216,7 +21352,7 @@
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="B9" s="6">
         <f>SUMIFS(03_rows!J2:J25,03_rows!B2:B25,"MUM-1-H4")-SUMIFS(03_rows!H2:H25,03_rows!B2:B25,"MUM-1-H4")</f>
@@ -21232,7 +21368,7 @@
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="B10" s="6">
         <f>COUNTIFS(07_cascade_result!K2:K13,"exceeded")</f>
@@ -21248,7 +21384,7 @@
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="B11" s="6">
         <f>COUNTIFS(07_cascade_result!K2:K13,"redundancy_lost")</f>
@@ -21264,7 +21400,7 @@
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="B12" s="6">
         <f>SUM(06_upgrade_options!D2:D7)</f>
@@ -21280,7 +21416,7 @@
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="B13" s="6">
         <f>MAX(06_upgrade_options!E2:E7)</f>
@@ -21296,7 +21432,7 @@
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="B14" s="6">
         <f>SUM(01_facilities!J2:J7)</f>
@@ -21312,7 +21448,7 @@
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="B15" s="6">
         <f>COUNTA(04_racks!A2:A481)</f>
@@ -21328,7 +21464,7 @@
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="B16" s="6">
         <f>ROUND(SUM(04_racks!N2:N481),0)</f>
@@ -21344,7 +21480,7 @@
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="B17" s="6">
         <f>COUNTIFS(04_racks!O2:O481,"occupied")</f>
@@ -21360,7 +21496,7 @@
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="B18" s="6">
         <f>COUNTIFS(04_racks!C2:C481,"MUM-1-H4",04_racks!O2:O481,"free")</f>
@@ -21376,7 +21512,7 @@
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="B19" s="6">
         <f>COUNTIFS(04_racks!O2:O481,"blocked")</f>
@@ -21392,7 +21528,7 @@
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="B20" s="6">
         <f>COUNTA(04b_component_positions!A2:A149)</f>
@@ -21408,7 +21544,7 @@
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
     </row>
   </sheetData>
@@ -21435,22 +21571,22 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>789</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>1577</v>
@@ -21459,30 +21595,30 @@
         <v>1831</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>831</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="F2" s="8">
         <v>1</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>1843</v>
@@ -21493,25 +21629,25 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>831</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="F3" s="8">
         <v>2</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>1843</v>
@@ -21522,25 +21658,25 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>831</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="F4" s="8">
         <v>3</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>1872</v>
@@ -21551,25 +21687,25 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>831</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="F5" s="8">
         <v>4</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>8</v>
@@ -21580,25 +21716,25 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>831</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="F6" s="8">
         <v>5</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>1843</v>
@@ -21609,25 +21745,25 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>989</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="F7" s="8">
         <v>1</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>8</v>
@@ -21638,25 +21774,25 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>989</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="F8" s="8">
         <v>2</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>8</v>
@@ -21667,25 +21803,25 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>989</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="F9" s="8">
         <v>3</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>8</v>
@@ -21696,25 +21832,25 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>989</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="F10" s="8">
         <v>4</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>1881</v>
@@ -21725,25 +21861,25 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>989</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="F11" s="8">
         <v>1</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>8</v>
@@ -21754,25 +21890,25 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>989</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="F12" s="8">
         <v>2</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>8</v>
@@ -21783,25 +21919,25 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>977</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="F13" s="8">
         <v>1</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>8</v>
@@ -21812,25 +21948,25 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>977</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="F14" s="8">
         <v>2</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>8</v>
@@ -21841,25 +21977,25 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>977</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="F15" s="8">
         <v>3</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>8</v>
@@ -21870,25 +22006,25 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>977</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="F16" s="8">
         <v>4</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>8</v>
@@ -21899,25 +22035,25 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>977</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="F17" s="8">
         <v>1</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>8</v>
@@ -21928,25 +22064,25 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>977</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="F18" s="8">
         <v>2</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>8</v>
@@ -21957,25 +22093,25 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>977</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="F19" s="8">
         <v>3</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>8</v>
@@ -21986,25 +22122,25 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>977</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="F20" s="8">
         <v>4</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>1886</v>
@@ -22015,25 +22151,25 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>970</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="F21" s="8">
         <v>1</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>8</v>
@@ -22044,25 +22180,25 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>970</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="F22" s="8">
         <v>2</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>8</v>
@@ -22073,25 +22209,25 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>970</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="F23" s="8">
         <v>3</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>8</v>
@@ -22102,25 +22238,25 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>970</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="F24" s="8">
         <v>1</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>1886</v>
@@ -22131,25 +22267,25 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>970</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="F25" s="8">
         <v>2</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>8</v>
@@ -22160,25 +22296,25 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>970</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="F26" s="8">
         <v>3</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>1886</v>
@@ -22189,25 +22325,25 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>982</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="F27" s="8">
         <v>1</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>8</v>
@@ -22218,25 +22354,25 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>982</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="F28" s="8">
         <v>2</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>8</v>
@@ -22247,25 +22383,25 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>851</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="F29" s="8">
         <v>1</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>1843</v>
@@ -22276,25 +22412,25 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>851</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="F30" s="8">
         <v>2</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>1843</v>
@@ -22305,25 +22441,25 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>851</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="F31" s="8">
         <v>3</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>1843</v>
@@ -22334,25 +22470,25 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>854</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>792</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="F32" s="8">
         <v>1</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>1881</v>
@@ -22363,25 +22499,25 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>854</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>792</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="F33" s="8">
         <v>2</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>1881</v>
@@ -22392,25 +22528,25 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>854</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>792</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="F34" s="8">
         <v>3</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>1881</v>
@@ -22421,25 +22557,25 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>818</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="F35" s="8">
         <v>1</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>8</v>
@@ -22450,25 +22586,25 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>818</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="F36" s="8">
         <v>2</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>1843</v>
@@ -22479,25 +22615,25 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>818</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="F37" s="8">
         <v>3</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>8</v>
@@ -22508,25 +22644,25 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>802</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>792</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="F38" s="8">
         <v>1</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>1881</v>
@@ -22537,25 +22673,25 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>802</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>792</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="F39" s="8">
         <v>2</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>1881</v>
@@ -22566,25 +22702,25 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>802</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>792</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="F40" s="8">
         <v>3</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>1872</v>
@@ -22595,25 +22731,25 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>1063</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>792</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="F41" s="8">
         <v>1</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>1881</v>
@@ -22624,25 +22760,25 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>1063</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>792</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="F42" s="8">
         <v>2</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>1881</v>
@@ -22653,17 +22789,17 @@
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
   </sheetData>
@@ -22692,25 +22828,25 @@
         <v>42</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -22718,7 +22854,7 @@
         <v>61</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="C2" s="8">
         <v>4</v>
@@ -22736,7 +22872,7 @@
         <v>18</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -22744,7 +22880,7 @@
         <v>69</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="C3" s="8">
         <v>4</v>
@@ -22762,7 +22898,7 @@
         <v>23</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -22770,7 +22906,7 @@
         <v>73</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="C4" s="8">
         <v>4</v>
@@ -22788,7 +22924,7 @@
         <v>27</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -22796,7 +22932,7 @@
         <v>79</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="C5" s="8">
         <v>3</v>
@@ -22814,7 +22950,7 @@
         <v>11</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -22822,7 +22958,7 @@
         <v>85</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="C6" s="8">
         <v>2</v>
@@ -22840,7 +22976,7 @@
         <v>34</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -22848,7 +22984,7 @@
         <v>91</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="C7" s="8">
         <v>3</v>
@@ -22862,22 +22998,22 @@
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
     </row>
   </sheetData>
@@ -22905,22 +23041,22 @@
         <v>789</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>800</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -22928,13 +23064,13 @@
         <v>831</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="E2" s="8">
         <v>16</v>
@@ -22943,7 +23079,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -22951,13 +23087,13 @@
         <v>854</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="E3" s="8">
         <v>10</v>
@@ -22966,7 +23102,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -22974,13 +23110,13 @@
         <v>847</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="E4" s="8">
         <v>9</v>
@@ -22989,7 +23125,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -22997,13 +23133,13 @@
         <v>851</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="E5" s="8">
         <v>14</v>
@@ -23012,7 +23148,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -23020,13 +23156,13 @@
         <v>989</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="E6" s="8">
         <v>8</v>
@@ -23035,7 +23171,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -23043,13 +23179,13 @@
         <v>977</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="E7" s="8">
         <v>22</v>
@@ -23058,7 +23194,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -23066,13 +23202,13 @@
         <v>970</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="E8" s="8">
         <v>12</v>
@@ -23081,7 +23217,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -23089,13 +23225,13 @@
         <v>982</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="E9" s="8">
         <v>6</v>
@@ -23104,7 +23240,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -23112,13 +23248,13 @@
         <v>818</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="E10" s="8">
         <v>26</v>
@@ -23127,7 +23263,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -23135,13 +23271,13 @@
         <v>812</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="E11" s="8">
         <v>34</v>
@@ -23150,7 +23286,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -23158,13 +23294,13 @@
         <v>826</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="E12" s="8">
         <v>20</v>
@@ -23173,17 +23309,17 @@
         <v>0</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
     </row>
   </sheetData>
@@ -23209,7 +23345,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>42</v>
@@ -23224,24 +23360,24 @@
         <v>788</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>61</v>
@@ -23256,7 +23392,7 @@
         <v>204</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G2" s="10">
         <v>21.3</v>
@@ -23266,12 +23402,12 @@
         <v>27</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>61</v>
@@ -23286,7 +23422,7 @@
         <v>216</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G3" s="10">
         <v>21.9</v>
@@ -23296,12 +23432,12 @@
         <v>27</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>61</v>
@@ -23316,7 +23452,7 @@
         <v>229</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G4" s="10">
         <v>21.3</v>
@@ -23326,12 +23462,12 @@
         <v>27</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>61</v>
@@ -23346,7 +23482,7 @@
         <v>241</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G5" s="8">
         <v>22</v>
@@ -23356,12 +23492,12 @@
         <v>27</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>61</v>
@@ -23376,7 +23512,7 @@
         <v>254</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G6" s="10">
         <v>20.9</v>
@@ -23386,12 +23522,12 @@
         <v>27</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>61</v>
@@ -23406,7 +23542,7 @@
         <v>266</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G7" s="10">
         <v>21.7</v>
@@ -23416,12 +23552,12 @@
         <v>27</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>61</v>
@@ -23436,7 +23572,7 @@
         <v>280</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G8" s="10">
         <v>21.1</v>
@@ -23446,12 +23582,12 @@
         <v>27</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>61</v>
@@ -23466,7 +23602,7 @@
         <v>292</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G9" s="8">
         <v>22</v>
@@ -23476,12 +23612,12 @@
         <v>27</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>61</v>
@@ -23496,7 +23632,7 @@
         <v>305</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G10" s="10">
         <v>20.9</v>
@@ -23506,12 +23642,12 @@
         <v>27</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>61</v>
@@ -23526,7 +23662,7 @@
         <v>317</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G11" s="10">
         <v>21.9</v>
@@ -23536,12 +23672,12 @@
         <v>27</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>61</v>
@@ -23556,7 +23692,7 @@
         <v>330</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G12" s="10">
         <v>20.8</v>
@@ -23566,12 +23702,12 @@
         <v>27</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>61</v>
@@ -23586,7 +23722,7 @@
         <v>342</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G13" s="10">
         <v>21.9</v>
@@ -23596,12 +23732,12 @@
         <v>27</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>61</v>
@@ -23616,7 +23752,7 @@
         <v>354</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G14" s="10">
         <v>21.6</v>
@@ -23626,12 +23762,12 @@
         <v>27</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>61</v>
@@ -23646,7 +23782,7 @@
         <v>366</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G15" s="10">
         <v>22.2</v>
@@ -23656,12 +23792,12 @@
         <v>27</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>61</v>
@@ -23676,7 +23812,7 @@
         <v>378</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G16" s="10">
         <v>21.2</v>
@@ -23686,12 +23822,12 @@
         <v>27</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>61</v>
@@ -23706,7 +23842,7 @@
         <v>390</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G17" s="10">
         <v>21.9</v>
@@ -23716,12 +23852,12 @@
         <v>27</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>61</v>
@@ -23736,7 +23872,7 @@
         <v>402</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G18" s="10">
         <v>21.1</v>
@@ -23746,12 +23882,12 @@
         <v>27</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>61</v>
@@ -23766,7 +23902,7 @@
         <v>414</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G19" s="10">
         <v>21.9</v>
@@ -23776,12 +23912,12 @@
         <v>27</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>61</v>
@@ -23796,7 +23932,7 @@
         <v>426</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G20" s="10">
         <v>20.9</v>
@@ -23806,12 +23942,12 @@
         <v>27</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>61</v>
@@ -23826,7 +23962,7 @@
         <v>438</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G21" s="10">
         <v>21.8</v>
@@ -23836,12 +23972,12 @@
         <v>27</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>61</v>
@@ -23856,7 +23992,7 @@
         <v>451</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G22" s="8">
         <v>22</v>
@@ -23866,12 +24002,12 @@
         <v>27</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>61</v>
@@ -23886,7 +24022,7 @@
         <v>463</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G23" s="8">
         <v>23</v>
@@ -23896,12 +24032,12 @@
         <v>27</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>61</v>
@@ -23916,7 +24052,7 @@
         <v>475</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G24" s="10">
         <v>20.9</v>
@@ -23926,12 +24062,12 @@
         <v>27</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>61</v>
@@ -23946,7 +24082,7 @@
         <v>487</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G25" s="8">
         <v>22</v>
@@ -23956,12 +24092,12 @@
         <v>27</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>61</v>
@@ -23976,7 +24112,7 @@
         <v>499</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G26" s="10">
         <v>21.2</v>
@@ -23986,12 +24122,12 @@
         <v>27</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>61</v>
@@ -24006,7 +24142,7 @@
         <v>511</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G27" s="10">
         <v>21.8</v>
@@ -24016,12 +24152,12 @@
         <v>27</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>61</v>
@@ -24036,7 +24172,7 @@
         <v>523</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G28" s="10">
         <v>21.1</v>
@@ -24046,12 +24182,12 @@
         <v>27</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>61</v>
@@ -24066,7 +24202,7 @@
         <v>535</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G29" s="10">
         <v>21.8</v>
@@ -24076,12 +24212,12 @@
         <v>27</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>61</v>
@@ -24096,7 +24232,7 @@
         <v>547</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G30" s="10">
         <v>20.9</v>
@@ -24106,12 +24242,12 @@
         <v>27</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>61</v>
@@ -24126,7 +24262,7 @@
         <v>559</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G31" s="10">
         <v>21.7</v>
@@ -24136,12 +24272,12 @@
         <v>27</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>61</v>
@@ -24156,7 +24292,7 @@
         <v>571</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G32" s="8">
         <v>21</v>
@@ -24166,12 +24302,12 @@
         <v>27</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>61</v>
@@ -24186,7 +24322,7 @@
         <v>583</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G33" s="10">
         <v>21.9</v>
@@ -24196,12 +24332,12 @@
         <v>27</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>61</v>
@@ -24216,7 +24352,7 @@
         <v>595</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G34" s="10">
         <v>20.9</v>
@@ -24226,12 +24362,12 @@
         <v>27</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>61</v>
@@ -24246,7 +24382,7 @@
         <v>607</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G35" s="10">
         <v>21.9</v>
@@ -24256,12 +24392,12 @@
         <v>27</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>61</v>
@@ -24276,7 +24412,7 @@
         <v>619</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G36" s="10">
         <v>20.7</v>
@@ -24286,12 +24422,12 @@
         <v>27</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>61</v>
@@ -24306,7 +24442,7 @@
         <v>631</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G37" s="10">
         <v>21.8</v>
@@ -24316,12 +24452,12 @@
         <v>27</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>61</v>
@@ -24336,7 +24472,7 @@
         <v>643</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G38" s="10">
         <v>22.6</v>
@@ -24346,12 +24482,12 @@
         <v>27</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>61</v>
@@ -24366,7 +24502,7 @@
         <v>655</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G39" s="10">
         <v>23.2</v>
@@ -24376,12 +24512,12 @@
         <v>27</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>61</v>
@@ -24396,7 +24532,7 @@
         <v>667</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G40" s="10">
         <v>22.3</v>
@@ -24406,12 +24542,12 @@
         <v>27</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>61</v>
@@ -24426,7 +24562,7 @@
         <v>679</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G41" s="8">
         <v>23</v>
@@ -24436,12 +24572,12 @@
         <v>27</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>61</v>
@@ -24456,7 +24592,7 @@
         <v>691</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G42" s="10">
         <v>22.3</v>
@@ -24466,12 +24602,12 @@
         <v>27</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>61</v>
@@ -24486,7 +24622,7 @@
         <v>703</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G43" s="10">
         <v>23.1</v>
@@ -24496,12 +24632,12 @@
         <v>27</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>61</v>
@@ -24516,7 +24652,7 @@
         <v>715</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G44" s="10">
         <v>22.1</v>
@@ -24526,12 +24662,12 @@
         <v>27</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>61</v>
@@ -24546,7 +24682,7 @@
         <v>727</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G45" s="8">
         <v>23</v>
@@ -24556,12 +24692,12 @@
         <v>27</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>61</v>
@@ -24576,7 +24712,7 @@
         <v>739</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G46" s="8">
         <v>22</v>
@@ -24586,12 +24722,12 @@
         <v>27</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>61</v>
@@ -24606,7 +24742,7 @@
         <v>751</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G47" s="8">
         <v>23</v>
@@ -24616,12 +24752,12 @@
         <v>27</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>61</v>
@@ -24636,7 +24772,7 @@
         <v>763</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G48" s="8">
         <v>22</v>
@@ -24646,12 +24782,12 @@
         <v>27</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>61</v>
@@ -24666,7 +24802,7 @@
         <v>775</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G49" s="10">
         <v>23.1</v>
@@ -24676,12 +24812,12 @@
         <v>27</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>61</v>
@@ -24696,7 +24832,7 @@
         <v>204</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G50" s="10">
         <v>17.7</v>
@@ -24708,12 +24844,12 @@
         <v>20</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>61</v>
@@ -24728,7 +24864,7 @@
         <v>216</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G51" s="10">
         <v>17.8</v>
@@ -24740,12 +24876,12 @@
         <v>20</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>61</v>
@@ -24760,7 +24896,7 @@
         <v>229</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G52" s="10">
         <v>17.9</v>
@@ -24772,12 +24908,12 @@
         <v>20</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>61</v>
@@ -24792,7 +24928,7 @@
         <v>241</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G53" s="8">
         <v>18</v>
@@ -24804,12 +24940,12 @@
         <v>20</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>61</v>
@@ -24824,7 +24960,7 @@
         <v>254</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G54" s="10">
         <v>18.1</v>
@@ -24836,12 +24972,12 @@
         <v>20</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>61</v>
@@ -24856,7 +24992,7 @@
         <v>266</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G55" s="10">
         <v>18.2</v>
@@ -24868,12 +25004,12 @@
         <v>20</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>61</v>
@@ -24888,7 +25024,7 @@
         <v>280</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G56" s="10">
         <v>18.3</v>
@@ -24900,12 +25036,12 @@
         <v>20</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>61</v>
@@ -24920,7 +25056,7 @@
         <v>292</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G57" s="10">
         <v>18.4</v>
@@ -24932,12 +25068,12 @@
         <v>20</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>61</v>
@@ -24952,7 +25088,7 @@
         <v>305</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G58" s="10">
         <v>17.6</v>
@@ -24964,12 +25100,12 @@
         <v>20</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>61</v>
@@ -24984,7 +25120,7 @@
         <v>317</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G59" s="10">
         <v>17.7</v>
@@ -24996,12 +25132,12 @@
         <v>20</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>61</v>
@@ -25016,7 +25152,7 @@
         <v>330</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G60" s="10">
         <v>17.8</v>
@@ -25028,12 +25164,12 @@
         <v>20</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>61</v>
@@ -25048,7 +25184,7 @@
         <v>342</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G61" s="10">
         <v>17.9</v>
@@ -25060,12 +25196,12 @@
         <v>20</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>61</v>
@@ -25080,7 +25216,7 @@
         <v>354</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G62" s="8">
         <v>18</v>
@@ -25092,12 +25228,12 @@
         <v>20</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>61</v>
@@ -25112,7 +25248,7 @@
         <v>366</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G63" s="10">
         <v>18.1</v>
@@ -25124,12 +25260,12 @@
         <v>20</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>61</v>
@@ -25144,7 +25280,7 @@
         <v>378</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G64" s="10">
         <v>18.2</v>
@@ -25156,12 +25292,12 @@
         <v>20</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>61</v>
@@ -25176,7 +25312,7 @@
         <v>390</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G65" s="10">
         <v>18.3</v>
@@ -25188,12 +25324,12 @@
         <v>20</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>61</v>
@@ -25208,7 +25344,7 @@
         <v>402</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G66" s="10">
         <v>18.4</v>
@@ -25220,12 +25356,12 @@
         <v>20</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>61</v>
@@ -25240,7 +25376,7 @@
         <v>414</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G67" s="10">
         <v>17.6</v>
@@ -25252,12 +25388,12 @@
         <v>20</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>61</v>
@@ -25272,7 +25408,7 @@
         <v>426</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G68" s="10">
         <v>17.7</v>
@@ -25284,12 +25420,12 @@
         <v>20</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>61</v>
@@ -25304,7 +25440,7 @@
         <v>438</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G69" s="10">
         <v>17.8</v>
@@ -25316,12 +25452,12 @@
         <v>20</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>61</v>
@@ -25336,7 +25472,7 @@
         <v>451</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G70" s="10">
         <v>20.1</v>
@@ -25348,12 +25484,12 @@
         <v>20</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>61</v>
@@ -25368,7 +25504,7 @@
         <v>463</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G71" s="8">
         <v>18</v>
@@ -25380,12 +25516,12 @@
         <v>20</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>61</v>
@@ -25400,7 +25536,7 @@
         <v>475</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G72" s="10">
         <v>18.1</v>
@@ -25412,12 +25548,12 @@
         <v>20</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>61</v>
@@ -25432,7 +25568,7 @@
         <v>487</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G73" s="10">
         <v>18.2</v>
@@ -25444,12 +25580,12 @@
         <v>20</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>61</v>
@@ -25464,7 +25600,7 @@
         <v>499</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G74" s="10">
         <v>18.3</v>
@@ -25476,12 +25612,12 @@
         <v>20</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>61</v>
@@ -25496,7 +25632,7 @@
         <v>511</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G75" s="10">
         <v>18.4</v>
@@ -25508,12 +25644,12 @@
         <v>20</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>61</v>
@@ -25528,7 +25664,7 @@
         <v>523</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G76" s="10">
         <v>17.6</v>
@@ -25540,12 +25676,12 @@
         <v>20</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>61</v>
@@ -25560,7 +25696,7 @@
         <v>535</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G77" s="10">
         <v>17.7</v>
@@ -25572,12 +25708,12 @@
         <v>20</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>61</v>
@@ -25592,7 +25728,7 @@
         <v>547</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G78" s="10">
         <v>17.8</v>
@@ -25604,12 +25740,12 @@
         <v>20</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>61</v>
@@ -25624,7 +25760,7 @@
         <v>559</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G79" s="10">
         <v>17.9</v>
@@ -25636,12 +25772,12 @@
         <v>20</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>61</v>
@@ -25656,7 +25792,7 @@
         <v>571</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G80" s="8">
         <v>18</v>
@@ -25668,12 +25804,12 @@
         <v>20</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>61</v>
@@ -25688,7 +25824,7 @@
         <v>583</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G81" s="10">
         <v>18.1</v>
@@ -25700,12 +25836,12 @@
         <v>20</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>61</v>
@@ -25720,7 +25856,7 @@
         <v>595</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G82" s="10">
         <v>18.2</v>
@@ -25732,12 +25868,12 @@
         <v>20</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>61</v>
@@ -25752,7 +25888,7 @@
         <v>607</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G83" s="10">
         <v>18.3</v>
@@ -25764,12 +25900,12 @@
         <v>20</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>61</v>
@@ -25784,7 +25920,7 @@
         <v>619</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G84" s="10">
         <v>18.4</v>
@@ -25796,12 +25932,12 @@
         <v>20</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>61</v>
@@ -25816,7 +25952,7 @@
         <v>631</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G85" s="10">
         <v>17.6</v>
@@ -25828,12 +25964,12 @@
         <v>20</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>61</v>
@@ -25848,7 +25984,7 @@
         <v>643</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G86" s="10">
         <v>17.7</v>
@@ -25860,12 +25996,12 @@
         <v>20</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>61</v>
@@ -25880,7 +26016,7 @@
         <v>655</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G87" s="10">
         <v>17.8</v>
@@ -25892,12 +26028,12 @@
         <v>20</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>61</v>
@@ -25912,7 +26048,7 @@
         <v>667</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G88" s="10">
         <v>17.9</v>
@@ -25924,12 +26060,12 @@
         <v>20</v>
       </c>
       <c r="J88" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>61</v>
@@ -25944,7 +26080,7 @@
         <v>679</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G89" s="8">
         <v>18</v>
@@ -25956,12 +26092,12 @@
         <v>20</v>
       </c>
       <c r="J89" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>61</v>
@@ -25976,7 +26112,7 @@
         <v>691</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G90" s="10">
         <v>18.1</v>
@@ -25988,12 +26124,12 @@
         <v>20</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>61</v>
@@ -26008,7 +26144,7 @@
         <v>703</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G91" s="10">
         <v>18.2</v>
@@ -26020,12 +26156,12 @@
         <v>20</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>61</v>
@@ -26040,7 +26176,7 @@
         <v>715</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G92" s="10">
         <v>18.3</v>
@@ -26052,12 +26188,12 @@
         <v>20</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>61</v>
@@ -26072,7 +26208,7 @@
         <v>727</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G93" s="10">
         <v>18.4</v>
@@ -26084,12 +26220,12 @@
         <v>20</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>61</v>
@@ -26104,7 +26240,7 @@
         <v>739</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G94" s="10">
         <v>17.6</v>
@@ -26116,12 +26252,12 @@
         <v>20</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>61</v>
@@ -26136,7 +26272,7 @@
         <v>751</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G95" s="10">
         <v>17.7</v>
@@ -26148,12 +26284,12 @@
         <v>20</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>61</v>
@@ -26168,7 +26304,7 @@
         <v>763</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G96" s="10">
         <v>17.8</v>
@@ -26180,12 +26316,12 @@
         <v>20</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>61</v>
@@ -26200,7 +26336,7 @@
         <v>775</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G97" s="10">
         <v>17.9</v>
@@ -26212,17 +26348,17 @@
         <v>20</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="9" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="9" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
     </row>
   </sheetData>
